--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09T20:54:48Z</t>
+          <t>2026-09-09T23:13:15Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-09-09T20:54:48Z · 529 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-09-09T23:13:15Z · 529 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>bcb3af284d3724c7</t>
+          <t>c47a04aef0c20457</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T20:54:48Z</t>
+          <t>2026-09-09T16:36:42Z</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The Tribune</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - The Tribune</t>
+          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage - The Rising Nepal</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing The Tribune</t>
+          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage The Rising Nepal</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzjSAcMBQVVfeXFMUDhDODZqTTIyNFlqeExnNGQyem9wcHNIN29fV3hQVVpXby1qZjl5akNSSi1YZ2lYVTZwTnhIT1h5aW1ocjFKbDd4N040cnhjU0lCMmFnUFd6RTlDdVI3cTRDZTEzX3k2TEFXZ2lCeVcxQW5jUnZCZ2YwN2JLQ01NTFp2OXBnOEV2R3NUNjdBSFQ1ZzBDUjVmRV9aQmFHY1E1c1g0UmwzOVVBckdDS2hGOVl3WlN3VEVLNHJmNENFSjl2cW84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzjSAcMBQVVfeXFMUDhDODZqTTIyNFlqeExnNGQyem9wcHNIN29fV3hQVVpXby1qZjl5akNSSi1YZ2lYVTZwTnhIT1h5aW1ocjFKbDd4N040cnhjU0lCMmFnUFd6RTlDdVI3cTRDZTEzX3k2TEFXZ2lCeVcxQW5jUnZCZ2YwN2JLQ01NTFp2OXBnOEV2R3NUNjdBSFQ1ZzBDUjVmRV9aQmFHY1E1c1g0UmwzOVVBckdDS2hGOVl3WlN3VEVLNHJmNENFSjl2cW84?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>f0d257c13960eb9d</t>
+          <t>bcb3af284d3724c7</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -723,32 +723,32 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T16:36:42Z</t>
+          <t>2026-09-09T20:54:48Z</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing - myRepublica</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing - The Tribune</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing myRepublica</t>
+          <t>Nepal issues DNA testing notice for overseas families of Bhotekoshi flood missing The Tribune</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzjSAcMBQVVfeXFMUDhDODZqTTIyNFlqeExnNGQyem9wcHNIN29fV3hQVVpXby1qZjl5akNSSi1YZ2lYVTZwTnhIT1h5aW1ocjFKbDd4N040cnhjU0lCMmFnUFd6RTlDdVI3cTRDZTEzX3k2TEFXZ2lCeVcxQW5jUnZCZ2YwN2JLQ01NTFp2OXBnOEV2R3NUNjdBSFQ1ZzBDUjVmRV9aQmFHY1E1c1g0UmwzOVVBckdDS2hGOVl3WlN3VEVLNHJmNENFSjl2cW84?oc=5</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQOEM4NmpNMjI0WWp4TGc0ZDJ6b3Bwc0g3b19XeFBVWldvLWpmOXlqQ1JKLVhnaVhVNnBOeEhPWHlpbWhyMUpsN3g3TjRyeGNTSUIyYWdQV3pFOUN1UjdxNENlMTNfeTZMQVdnaUJ5VzFBbmNSdkJnZjA3YktDTU1MWnY5cGc4RXZHc1Q2N0FIVDVnMENSNWZFX1pCYUdjUTVzWDRSbDM5VUFyR0NLaEY5WXdaU3dURUs0cmY0Q0VKOXZxbzjSAcMBQVVfeXFMUDhDODZqTTIyNFlqeExnNGQyem9wcHNIN29fV3hQVVpXby1qZjl5akNSSi1YZ2lYVTZwTnhIT1h5aW1ocjFKbDd4N040cnhjU0lCMmFnUFd6RTlDdVI3cTRDZTEzX3k2TEFXZ2lCeVcxQW5jUnZCZ2YwN2JLQ01NTFp2OXBnOEV2R3NUNjdBSFQ1ZzBDUjVmRV9aQmFHY1E1c1g0UmwzOVVBckdDS2hGOVl3WlN3VEVLNHJmNENFSjl2cW84?oc=5</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>43b44149e2b39c71</t>
+          <t>f0d257c13960eb9d</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -780,27 +780,27 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing - Nepalnews.com</t>
+          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing - myRepublica</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing Nepalnews.com</t>
+          <t>Lawmakers urge full mobilization of state mechanisms to search for Bhotekoshi flood missing myRepublica</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxPenRzYlN2SktfbEh1aEJPOFRaNnlzSGR6cEtGVUxyUExWd29JcVZrRHNDZkN5d0lGSzJEaVBMbzhMcF95R2NpNm45bUM5Y0FTbzlOQm5QbjRPQW4xX2ctVVgxblFUMHVxc29NWDJ3ZTZqVFV0VVJ5UFB3TUtUU3VOam0ySlJCWjlFZmpyNXhsREY2dHFramp0QjR2V3Vnc2h4QnRfbVdzcEdUMUpEcEpHZ0ktZzNsNURyblphUkJ3REFwZy1YM21lVUF3?oc=5</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>c47a04aef0c20457</t>
+          <t>43b44149e2b39c71</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -832,27 +832,27 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage - The Rising Nepal</t>
+          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage The Rising Nepal</t>
+          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5hZ3dzYkIzQ2xHQkdyNWFManJNYUxPNzNNUEQ2MmtMTGVYb1ZkbVpBVTRYbm4yb1hFRjF5ZVh1MWt0WlFTN0pKV1ViQWJWR052?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisgFBVV95cUxOVWowcV9SaVBYTlpJLXRvdDh6R3ZTQ2hZWF9kUWRPRS1kc3hZd0pkdno3ZlRPMnJKd3Y3c01qaW1uV09PRGdpQmpTT1dlTmpiMExwMzhVM0JRZ3VuX1dhVEEyNkY0NXMxUDQyLTM5c0QtVUlLLTVDRE54WVcxc2RZbzdlSGFnVHk1T2lPUHlkVUthUjVtVGU4TGRvdG9ENmFnT1JpTk9DS3A3SjZfMGZNTzF3?oc=5</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>consultaelectoral.onpe.gob.pe</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - consultaelectoral.onpe.gob.pe</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) consultaelectoral.onpe.gob.pe</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 7 (As of 8 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2288,17 +2288,17 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Himal Southasian</t>
+          <t>himalmag.com</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>The climate warning from Nepal’s Rasuwa flood disaster - Himal Southasian</t>
+          <t>The climate warning from Nepal’s Rasuwa flood disaster - himalmag.com</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>The climate warning from Nepal’s Rasuwa flood disaster Himal Southasian</t>
+          <t>The climate warning from Nepal’s Rasuwa flood disaster himalmag.com</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>consultaelectoral.onpe.gob.pe</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Nepal Rasuwa Flood Situation Report No. 6 - consultaelectoral.onpe.gob.pe</t>
+          <t>Nepal Rasuwa Flood Situation Report No. 6 - ReliefWeb</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Nepal Rasuwa Flood Situation Report No. 6 consultaelectoral.onpe.gob.pe</t>
+          <t>Nepal Rasuwa Flood Situation Report No. 6 ReliefWeb</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -3120,17 +3120,17 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>consultaelectoral.onpe.gob.pe</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - consultaelectoral.onpe.gob.pe</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) consultaelectoral.onpe.gob.pe</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>consultaelectoral.onpe.gob.pe</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) - consultaelectoral.onpe.gob.pe</t>
+          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) consultaelectoral.onpe.gob.pe</t>
+          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -3796,17 +3796,17 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>consultaelectoral.onpe.gob.pe</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 - consultaelectoral.onpe.gob.pe</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 consultaelectoral.onpe.gob.pe</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 ReliefWeb</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -4108,17 +4108,17 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>The Farsight Nepal</t>
+          <t>farsightnepal.com</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll: 1,252, over 4,200 still missing - The Farsight Nepal</t>
+          <t>Bhotekoshi flood death toll: 1,252, over 4,200 still missing - farsightnepal.com</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll: 1,252, over 4,200 still missing The Farsight Nepal</t>
+          <t>Bhotekoshi flood death toll: 1,252, over 4,200 still missing farsightnepal.com</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
@@ -5148,17 +5148,17 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>South Asia Network on Dams, Rivers and People</t>
+          <t>sandrp.in</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>DRP 310826: Nepal’s Rasuwa flood disaster: Is there a limit to Human Folly? - South Asia Network on Dams, Rivers and People</t>
+          <t>DRP 310826: Nepal’s Rasuwa flood disaster: Is there a limit to Human Folly? - sandrp.in</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>DRP 310826: Nepal’s Rasuwa flood disaster: Is there a limit to Human Folly? South Asia Network on Dams, Rivers and People</t>
+          <t>DRP 310826: Nepal’s Rasuwa flood disaster: Is there a limit to Human Folly? sandrp.in</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>consultaelectoral.onpe.gob.pe</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Satellite-Detected Newly Formed Barrier Lakes Following an Ice-Rock Avalanche in Rasuwa District, Nepal, as of 28 August 2026 (Imagery Analysis: 26&amp;27/08/2026 Published: 27/08/2026 V1) consultaelectoral.onpe.gob.pe</t>
+          <t>Satellite-Detected Newly Formed Barrier Lakes Following an Ice-Rock Avalanche in Rasuwa District, Nepal, as of 28 August 2026 (Imagery Analysis: 26&amp;27/08/2026 Published: 27/08/2026 V1) ReliefWeb</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11T20:56:34Z</t>
+          <t>2026-09-11T23:15:11Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-09-11T20:56:34Z · 549 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-09-11T23:15:11Z · 549 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -676,17 +676,17 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>USV Pharma donates Rs 15M to Bhotekoshi flood victims through NMA - risingnepaldaily.com</t>
+          <t>USV Pharma donates Rs 15M to Bhotekoshi flood victims through NMA - The Rising Nepal</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>USV Pharma donates Rs 15M to Bhotekoshi flood victims through NMA risingnepaldaily.com</t>
+          <t>USV Pharma donates Rs 15M to Bhotekoshi flood victims through NMA The Rising Nepal</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>86baaa8f62a4528b</t>
+          <t>9b5c642e492710ec</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -780,27 +780,27 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion - myRepublica</t>
+          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone - Khabarhub</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion myRepublica</t>
+          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone Khabarhub</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkI1WExEWHVWU1RicWxEWFRvU01kbm81ekZQVjhDSUg0QzkzMDRnV1JjM19RSDdNS2RuVlY4Y1N1akZfRldxb291cVBrOGluamtjNnpNbjBVVDlHUUpmLXNNSGtXaHhKQzVzeWwtR2RYajg4NmtNdnJERmhUMWpuMmstel9CamkzOXdSR01TcHF2bW9aeFc3amFBeW9JWG1sSEVxNDdaWHdndmJrTE9xUU44UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9JSWlVZlMzUHNHS3N0d3BsUDl5VXc2aXFYMWFtWmg2ZDA4dURWemtRSVpKb3FBMHdGd2J5T0R5aFBwS0o2elR5OTlDR19MM0lDRG84a2ozWjg?oc=5</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkI1WExEWHVWU1RicWxEWFRvU01kbm81ekZQVjhDSUg0QzkzMDRnV1JjM19RSDdNS2RuVlY4Y1N1akZfRldxb291cVBrOGluamtjNnpNbjBVVDlHUUpmLXNNSGtXaHhKQzVzeWwtR2RYajg4NmtNdnJERmhUMWpuMmstel9CamkzOXdSR01TcHF2bW9aeFc3amFBeW9JWG1sSEVxNDdaWHdndmJrTE9xUU44UQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9JSWlVZlMzUHNHS3N0d3BsUDl5VXc2aXFYMWFtWmg2ZDA4dURWemtRSVpKb3FBMHdGd2J5T0R5aFBwS0o2elR5OTlDR19MM0lDRG84a2ozWjg?oc=5</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>9b5c642e492710ec</t>
+          <t>d0d766933140860c</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -837,22 +837,22 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone - Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,377 - Khabarhub</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,377 Khabarhub</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9JSWlVZlMzUHNHS3N0d3BsUDl5VXc2aXFYMWFtWmg2ZDA4dURWemtRSVpKb3FBMHdGd2J5T0R5aFBwS0o2elR5OTlDR19MM0lDRG84a2ozWjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ILUZtTXhTRTRJbnZHdEtEMWNfV3JRSjgtWjBRWmdyeEZMcVFYeW9OS0kza0V0aFRBcThLc2M4Wi1MSnFiMkFSYjRRekx1V3JLTVFoMUJMNGU?oc=5</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE9JSWlVZlMzUHNHS3N0d3BsUDl5VXc2aXFYMWFtWmg2ZDA4dURWemtRSVpKb3FBMHdGd2J5T0R5aFBwS0o2elR5OTlDR19MM0lDRG84a2ozWjg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ILUZtTXhTRTRJbnZHdEtEMWNfV3JRSjgtWjBRWmdyeEZMcVFYeW9OS0kza0V0aFRBcThLc2M4Wi1MSnFiMkFSYjRRekx1V3JLTVFoMUJMNGU?oc=5</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>d0d766933140860c</t>
+          <t>a75b589881133382</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -884,27 +884,27 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>The Climate Watch</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,377 - Khabarhub</t>
+          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood - The Climate Watch</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,377 Khabarhub</t>
+          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood The Climate Watch</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ILUZtTXhTRTRJbnZHdEtEMWNfV3JRSjgtWjBRWmdyeEZMcVFYeW9OS0kza0V0aFRBcThLc2M4Wi1MSnFiMkFSYjRRekx1V3JLTVFoMUJMNGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3h5TmtvV1BTdHZ4bG1OUHlwSzFOdVFuUDBqQjJzNlpvRGN5U0hpSnI2NEZCR1VxREEyRHlrZjFQOVN6OVZWVmh5VzhyZFRLUldXNTdQTWRteDltU3JSamFtMWlIUFR0TGctU0hIandTR1NqOGFQcUZ1X2VRTXAwLVNJQ01TNnRDTnZ1dG5ucjVBTTEwdm55cg?oc=5</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTE1ILUZtTXhTRTRJbnZHdEtEMWNfV3JRSjgtWjBRWmdyeEZMcVFYeW9OS0kza0V0aFRBcThLc2M4Wi1MSnFiMkFSYjRRekx1V3JLTVFoMUJMNGU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3h5TmtvV1BTdHZ4bG1OUHlwSzFOdVFuUDBqQjJzNlpvRGN5U0hpSnI2NEZCR1VxREEyRHlrZjFQOVN6OVZWVmh5VzhyZFRLUldXNTdQTWRteDltU3JSamFtMWlIUFR0TGctU0hIandTR1NqOGFQcUZ1X2VRTXAwLVNJQ01TNnRDTnZ1dG5ucjVBTTEwdm55cg?oc=5</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>a75b589881133382</t>
+          <t>86baaa8f62a4528b</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -936,27 +936,27 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>The Climate Watch</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood - The Climate Watch</t>
+          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion - myRepublica</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Nepal says $4.74 billion needed to rebuild after Bhotekoshi flood The Climate Watch</t>
+          <t>Bhotekoshi flood debris removal to cost over Rs 94 billion myRepublica</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3h5TmtvV1BTdHZ4bG1OUHlwSzFOdVFuUDBqQjJzNlpvRGN5U0hpSnI2NEZCR1VxREEyRHlrZjFQOVN6OVZWVmh5VzhyZFRLUldXNTdQTWRteDltU3JSamFtMWlIUFR0TGctU0hIandTR1NqOGFQcUZ1X2VRTXAwLVNJQ01TNnRDTnZ1dG5ucjVBTTEwdm55cg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkI1WExEWHVWU1RicWxEWFRvU01kbm81ekZQVjhDSUg0QzkzMDRnV1JjM19RSDdNS2RuVlY4Y1N1akZfRldxb291cVBrOGluamtjNnpNbjBVVDlHUUpmLXNNSGtXaHhKQzVzeWwtR2RYajg4NmtNdnJERmhUMWpuMmstel9CamkzOXdSR01TcHF2bW9aeFc3amFBeW9JWG1sSEVxNDdaWHdndmJrTE9xUU44UQ?oc=5</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3h5TmtvV1BTdHZ4bG1OUHlwSzFOdVFuUDBqQjJzNlpvRGN5U0hpSnI2NEZCR1VxREEyRHlrZjFQOVN6OVZWVmh5VzhyZFRLUldXNTdQTWRteDltU3JSamFtMWlIUFR0TGctU0hIandTR1NqOGFQcUZ1X2VRTXAwLVNJQ01TNnRDTnZ1dG5ucjVBTTEwdm55cg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkI1WExEWHVWU1RicWxEWFRvU01kbm81ekZQVjhDSUg0QzkzMDRnV1JjM19RSDdNS2RuVlY4Y1N1akZfRldxb291cVBrOGluamtjNnpNbjBVVDlHUUpmLXNNSGtXaHhKQzVzeWwtR2RYajg4NmtNdnJERmhUMWpuMmstel9CamkzOXdSR01TcHF2bW9aeFc3amFBeW9JWG1sSEVxNDdaWHdndmJrTE9xUU44UQ?oc=5</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims - risingnepaldaily.com</t>
+          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims - The Rising Nepal</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims risingnepaldaily.com</t>
+          <t>11,111 lamps lit in Bouddhanath in memory of Bhotekoshi flood victims The Rising Nepal</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage - risingnepaldaily.com</t>
+          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage - The Rising Nepal</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage risingnepaldaily.com</t>
+          <t>Finance Minister instructs for realistic assessment of Bhotekoshi flood damage The Rising Nepal</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far - risingnepaldaily.com</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far - The Rising Nepal</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,367 bodies recovered so far risingnepaldaily.com</t>
+          <t>Bhotekoshi flood: 1,367 bodies recovered so far The Rising Nepal</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Sub-committee formed to study about Rasuwa flood impacts - risingnepaldaily.com</t>
+          <t>Sub-committee formed to study about Rasuwa flood impacts - The Rising Nepal</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Sub-committee formed to study about Rasuwa flood impacts risingnepaldaily.com</t>
+          <t>Sub-committee formed to study about Rasuwa flood impacts The Rising Nepal</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk - risingnepaldaily.com</t>
+          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk - The Rising Nepal</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk risingnepaldaily.com</t>
+          <t>Bhotekoshi flood disrupts China trade route, festival supplies at risk The Rising Nepal</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Why Is the Identification of the Bodies Being Delayed? Understand It Through Five Questions - ekantipur.com</t>
+          <t>Bhotekoshi Flood: Why Is the Identification of the Bodies Being Delayed? Understand It Through Five Questions - Ekantipur</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: Why Is the Identification of the Bodies Being Delayed? Understand It Through Five Questions ekantipur.com</t>
+          <t>Bhotekoshi Flood: Why Is the Identification of the Bodies Being Delayed? Understand It Through Five Questions Ekantipur</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="61" ht="48" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>62c63745290773df</t>
+          <t>d74bb8f9671ee40d</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -3536,27 +3536,27 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood - myRepublica</t>
+          <t>Nepal Rasuwa Flood Situation Report No. 6 - ReliefWeb</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood myRepublica</t>
+          <t>Nepal Rasuwa Flood Situation Report No. 6 ReliefWeb</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNSHZGWWE3LU02dDMyTUl3VW0yZUpJdGN5c3hEVmd3M3EzMXVpakphU25rRGJWcnYwbzlneE4wNnJIMnRqdEVDWHhGX0toTEJnVmx0c1ZoRG5mZ2U2aEY5ekh1LWwwa09LNmhPdWJFbmVyNVlIQzZ3N2UxdDBlcjc4bA?oc=5</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxNSHZGWWE3LU02dDMyTUl3VW0yZUpJdGN5c3hEVmd3M3EzMXVpakphU25rRGJWcnYwbzlneE4wNnJIMnRqdEVDWHhGX0toTEJnVmx0c1ZoRG5mZ2U2aEY5ekh1LWwwa09LNmhPdWJFbmVyNVlIQzZ3N2UxdDBlcjc4bA?oc=5</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>d74bb8f9671ee40d</t>
+          <t>d8f9de0510371c12</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-09T04:38:51Z</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -3593,22 +3593,22 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Nepal Rasuwa Flood Situation Report No. 6 - ReliefWeb</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Nepal Rasuwa Flood Situation Report No. 6 ReliefWeb</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNSHZGWWE3LU02dDMyTUl3VW0yZUpJdGN5c3hEVmd3M3EzMXVpakphU25rRGJWcnYwbzlneE4wNnJIMnRqdEVDWHhGX0toTEJnVmx0c1ZoRG5mZ2U2aEY5ekh1LWwwa09LNmhPdWJFbmVyNVlIQzZ3N2UxdDBlcjc4bA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMigAFBVV95cUxNSHZGWWE3LU02dDMyTUl3VW0yZUpJdGN5c3hEVmd3M3EzMXVpakphU25rRGJWcnYwbzlneE4wNnJIMnRqdEVDWHhGX0toTEJnVmx0c1ZoRG5mZ2U2aEY5ekh1LWwwa09LNmhPdWJFbmVyNVlIQzZ3N2UxdDBlcjc4bA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="63" ht="48" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>d8f9de0510371c12</t>
+          <t>b42da176f0e827b6</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -3635,32 +3635,32 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:51Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - ReliefWeb</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) ReliefWeb</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKb9IBXEFVX3lxTE1hV1dRMm45NFFlZlpxU3hkVnlxWFh1WDQ4ay1PR3lIc2dEeE9aTWRoVzRSNWdna1hVdlZ6VmR4RG5HWk1UdVhuRDVydjlLVUNTYVNNNGh1MkZRb1J4?oc=5</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMilwFBVV95cUxPOTB1TnV0RVFFZlRyeWp5VWszUlFGZ1ZxdzhiTWdOTGZlc21tOHFva2ZlUXJTaFJOM0JEc0lPQ3FTMG9DOVpGTzZKaEN1SERpTnJRb2YtUk16QTFrVF84VWRJU3ZlNGI1RVctQkkwWHQ3LWl6UExKVlRCVlExRzVFeEIwbzhnMTktUll2eWg4UmV6WlFMa1Rv?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKb9IBXEFVX3lxTE1hV1dRMm45NFFlZlpxU3hkVnlxWFh1WDQ4ay1PR3lIc2dEeE9aTWRoVzRSNWdna1hVdlZ6VmR4RG5HWk1UdVhuRDVydjlLVUNTYVNNNGh1MkZRb1J4?oc=5</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>b42da176f0e827b6</t>
+          <t>d14614d3e2803615</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -3687,32 +3687,32 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
+          <t>Bhotekoshi Flood Update: 1,344 bodies recovered, search and rescue efforts ongoing - The Rising Nepal</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
+          <t>Bhotekoshi Flood Update: 1,344 bodies recovered, search and rescue efforts ongoing The Rising Nepal</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKb9IBXEFVX3lxTE1hV1dRMm45NFFlZlpxU3hkVnlxWFh1WDQ4ay1PR3lIc2dEeE9aTWRoVzRSNWdna1hVdlZ6VmR4RG5HWk1UdVhuRDVydjlLVUNTYVNNNGh1MkZRb1J4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tTGNDV2J1amJ0UFB5N3RjOW02N1ZwdHd4SDdQMlJHOVF3dWJ3M2VyRmlyS1drUTdadXUtSkhoSmp1RHA4bUlTVmpWY0tSYWp0?oc=5</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKb9IBXEFVX3lxTE1hV1dRMm45NFFlZlpxU3hkVnlxWFh1WDQ4ay1PR3lIc2dEeE9aTWRoVzRSNWdna1hVdlZ6VmR4RG5HWk1UdVhuRDVydjlLVUNTYVNNNGh1MkZRb1J4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tTGNDV2J1amJ0UFB5N3RjOW02N1ZwdHd4SDdQMlJHOVF3dWJ3M2VyRmlyS1drUTdadXUtSkhoSmp1RHA4bUlTVmpWY0tSYWp0?oc=5</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3729,7 +3729,7 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>d14614d3e2803615</t>
+          <t>7ac8c48d235b6902</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-05T22:53:38Z</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Update: 1,344 bodies recovered, search and rescue efforts ongoing - risingnepaldaily.com</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myRepublica</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood Update: 1,344 bodies recovered, search and rescue efforts ongoing risingnepaldaily.com</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myRepublica</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tTGNDV2J1amJ0UFB5N3RjOW02N1ZwdHd4SDdQMlJHOVF3dWJ3M2VyRmlyS1drUTdadXUtSkhoSmp1RHA4bUlTVmpWY0tSYWp0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tTGNDV2J1amJ0UFB5N3RjOW02N1ZwdHd4SDdQMlJHOVF3dWJ3M2VyRmlyS1drUTdadXUtSkhoSmp1RHA4bUlTVmpWY0tSYWp0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>7ac8c48d235b6902</t>
+          <t>f7c2e6ce3f764d01</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T22:53:38Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -3801,22 +3801,22 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myRepublica</t>
+          <t>Where does the money raised for Bhotekoshi flood victims go? - myRepublica</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myRepublica</t>
+          <t>Where does the money raised for Bhotekoshi flood victims go? myRepublica</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitwFBVV95cUxPdlQ3dEh1M0NsMkljNHAxcG5sNlM4WEdQM25WaFdlWFZLc0ZEM1ZtenBPQi1RTkx0elY3UDJJZVdHdS1KZDJXWUlyNHlRQVZURk9pc1VLWEp4SFRmZWtkZElWTXQ3MGQ1RDZlbk9QTFRWcnRxYXFsc19KcmE4U0E3Rnl1VDRIRjQwdEpUSXdNM1c1N1N4bUxUU3dtRFdpLUVjSkxQOGx2enAyZGNlelRDUkxMTnNBSFU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3885,7 +3885,7 @@
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>6c94171fc3f8e00c</t>
+          <t>65516a3eea842847</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
@@ -3895,32 +3895,32 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>ReliefWeb</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 - risingnepaldaily.com</t>
+          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 risingnepaldaily.com</t>
+          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) ReliefWeb</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxORW9zMnllcXlQYU9yd3E5ajlYMlFBalF2TFNnWlMyMVdFYm92aFBDZDVZMEQ5dFRxU2hmdGdHRGg3UU01cjVQZVVWNTVadHpveFVncW1mb2ZNMXdpeVc2VTViS1NsLW94S2VqZDNXMlc5SGtpSTMtMkR3TGdRSktXcXo2Z1ZlMDlCbG13?oc=5</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiiwFBVV95cUxORW9zMnllcXlQYU9yd3E5ajlYMlFBalF2TFNnWlMyMVdFYm92aFBDZDVZMEQ5dFRxU2hmdGdHRGg3UU01cjVQZVVWNTVadHpveFVncW1mb2ZNMXdpeVc2VTViS1NsLW94S2VqZDNXMlc5SGtpSTMtMkR3TGdRSktXcXo2Z1ZlMDlCbG13?oc=5</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>65516a3eea842847</t>
+          <t>b80549513c064b0f</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -3947,32 +3947,32 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-08T04:32:23Z</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) - ReliefWeb</t>
+          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) ReliefWeb</t>
+          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxORW9zMnllcXlQYU9yd3E5ajlYMlFBalF2TFNnWlMyMVdFYm92aFBDZDVZMEQ5dFRxU2hmdGdHRGg3UU01cjVQZVVWNTVadHpveFVncW1mb2ZNMXdpeVc2VTViS1NsLW94S2VqZDNXMlc5SGtpSTMtMkR3TGdRSktXcXo2Z1ZlMDlCbG13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiiwFBVV95cUxORW9zMnllcXlQYU9yd3E5ajlYMlFBalF2TFNnWlMyMVdFYm92aFBDZDVZMEQ5dFRxU2hmdGdHRGg3UU01cjVQZVVWNTVadHpveFVncW1mb2ZNMXdpeVc2VTViS1NsLW94S2VqZDNXMlc5SGtpSTMtMkR3TGdRSktXcXo2Z1ZlMDlCbG13?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' - risingnepaldaily.com</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' risingnepaldaily.com</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>How Much International Aid Arrived After the Bhotekoshi Flood? - ekantipur.com</t>
+          <t>How Much International Aid Arrived After the Bhotekoshi Flood? - Ekantipur</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>How Much International Aid Arrived After the Bhotekoshi Flood? ekantipur.com</t>
+          <t>How Much International Aid Arrived After the Bhotekoshi Flood? Ekantipur</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>risingnepaldaily.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,204 bodies retrieved - risingnepaldaily.com</t>
+          <t>Bhotekoshi flood: 1,204 bodies retrieved - The Rising Nepal</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,204 bodies retrieved risingnepaldaily.com</t>
+          <t>Bhotekoshi flood: 1,204 bodies retrieved The Rising Nepal</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -4784,17 +4784,17 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>timesofindia.indiatimes.com</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September - timesofindia.indiatimes.com</t>
+          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September - The Times of India</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September timesofindia.indiatimes.com</t>
+          <t>‘Not Charity, But Justice’: Nepal To Raise Bhotekoshi Flood Compensation Demand At UNGA In September The Times of India</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -4836,17 +4836,17 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>timesofindia.indiatimes.com</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood 'serious signal' of rising climate risks, says Nepal PM Shah urging global action - timesofindia.indiatimes.com</t>
+          <t>Bhotekoshi flood 'serious signal' of rising climate risks, says Nepal PM Shah urging global action - The Times of India</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood 'serious signal' of rising climate risks, says Nepal PM Shah urging global action timesofindia.indiatimes.com</t>
+          <t>Bhotekoshi flood 'serious signal' of rising climate risks, says Nepal PM Shah urging global action The Times of India</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>ekantipur.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 21 People from Samitipur Missing Inside the Upper Trishuli–1 Tunnel - ekantipur.com</t>
+          <t>Bhotekoshi Flood: 21 People from Samitipur Missing Inside the Upper Trishuli–1 Tunnel - Ekantipur</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 21 People from Samitipur Missing Inside the Upper Trishuli–1 Tunnel ekantipur.com</t>
+          <t>Bhotekoshi Flood: 21 People from Samitipur Missing Inside the Upper Trishuli–1 Tunnel Ekantipur</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -5200,17 +5200,17 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>watchers.news</t>
+          <t>The Watchers - Watching the world evolve and transform</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood reconstruction may cost USD 4–5 billion, death toll rises to 675 - watchers.news</t>
+          <t>Bhote Koshi flood reconstruction may cost USD 4–5 billion, death toll rises to 675 - The Watchers - Watching the world evolve and transform</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood reconstruction may cost USD 4–5 billion, death toll rises to 675 watchers.news</t>
+          <t>Bhote Koshi flood reconstruction may cost USD 4–5 billion, death toll rises to 675 The Watchers - Watching the world evolve and transform</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -7993,7 +7993,7 @@
     <row r="147" ht="48" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>0370f1426397bded</t>
+          <t>62c63745290773df</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
+          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood - myRepublica</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
+          <t>Four Australian nationals of Indian origin missing in Bhotekoshi flood myRepublica</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKbw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2N4OXFNR3RtWkhqYW5BYmZKbktPakJ5VjhoNzJ0RVJNZmYyYkdzYXdRcVEzRDBfczdPTW1RVHUtYlBSZ2FYaW1zRlYydXlrc0ltRjN5N2w3NVZWclFCcDFTc2F5LXdZZ2ZOdFM4WEx0bktsUUh6VF83TlJfUDVGLXh4MzJLVHl3MHBYdnJZdzY2Z1BxZmp2bHA5dUZCMlBtWG84RzZLd0hIS0dpbzBmNzV0UXpGWUV1d2ZLT0ZyV3h0WUU?oc=5</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8045,7 +8045,7 @@
     <row r="148" ht="48" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>f805b0f8b9633407</t>
+          <t>0370f1426397bded</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T17:19:49Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>The Himalayan Times</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>64-year-old woman rescued alive on 11th day after Bhotekoshi flood – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>64-year-old woman rescued alive on 11th day after Bhotekoshi flood – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5pSEluMnhRZjNXVTFrZUt2T3ZEVHI3QnVURjl5aFlhdGlkcjZBRmRGVUNsS0hJUTMtQV9RRVp2aE5NQWI4UVVPSGgzQkZ4Wm8za2cyY3FadmlwcWRuRjFCUXdNUzE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKbw?oc=5</t>
         </is>
       </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5pSEluMnhRZjNXVTFrZUt2T3ZEVHI3QnVURjl5aFlhdGlkcjZBRmRGVUNsS0hJUTMtQV9RRVp2aE5NQWI4UVVPSGgzQkZ4Wm8za2cyY3FadmlwcWRuRjFCUXdNUzE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxQX3gzY0FSXzdYNjBMVXlicG1IRTBMS25lMWpEOVZKX1E3aU1jZVNGYldTTGFqWFpRamV3NUx4d3RkTUtiTmZlbTEyV003ZFVJNEdBM0ZqcUxVSmMtUkI4MC1neTUzeUJSZWFFd1dPWXJCQWhHUW13a3A1RXBuaWJiVEQ1eW5yUVIyRm9ZUWd5V0VlR2tyMzJqOWRKbw?oc=5</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -8097,7 +8097,7 @@
     <row r="149" ht="48" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>f7c2e6ce3f764d01</t>
+          <t>f805b0f8b9633407</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
@@ -8107,32 +8107,32 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-05T17:19:49Z</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Where does the money raised for Bhotekoshi flood victims go? - myRepublica</t>
+          <t>64-year-old woman rescued alive on 11th day after Bhotekoshi flood – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Where does the money raised for Bhotekoshi flood victims go? myRepublica</t>
+          <t>64-year-old woman rescued alive on 11th day after Bhotekoshi flood – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5pSEluMnhRZjNXVTFrZUt2T3ZEVHI3QnVURjl5aFlhdGlkcjZBRmRGVUNsS0hJUTMtQV9RRVp2aE5NQWI4UVVPSGgzQkZ4Wm8za2cyY3FadmlwcWRuRjFCUXdNUzE?oc=5</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMitAFBVV95cUxNY2txa3RLTTk3VzVubEZxcWotR3JJYmFtT2RfMDFqLWxtZFphb3Y5WDdobjhqMV9KWm1IbTdGb25ybGZQemxxLS1Nb1FWaEQ4aEhyWWZvWjFQOWtEY0RZNThBbVpZQXlSQTlVRjdTWEo2c0FndjFZSTY0WjJlalQ3d0EwSkVjaHFWc0V1eFJXQ09kMk5FOTZhcXdoZVR1LXh5NVdpemtJZnRvMHhNZXM5X1dDZF8?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE5pSEluMnhRZjNXVTFrZUt2T3ZEVHI3QnVURjl5aFlhdGlkcjZBRmRGVUNsS0hJUTMtQV9RRVp2aE5NQWI4UVVPSGgzQkZ4Wm8za2cyY3FadmlwcWRuRjFCUXdNUzE?oc=5</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
     <row r="161" ht="48" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>2c151d9781807ab6</t>
+          <t>6c94171fc3f8e00c</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
@@ -8731,32 +8731,32 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>risingnepaldaily.com</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital - The Rising Nepal</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 - risingnepaldaily.com</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital The Rising Nepal</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 risingnepaldaily.com</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
         </is>
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -8773,7 +8773,7 @@
     <row r="162" ht="48" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>02f3fec961d30051</t>
+          <t>2c151d9781807ab6</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -8793,22 +8793,22 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>NRCS marking 64th anniversary; mobilizes 5,000 volunteers in Bhotekoshi flood-hit area - The Rising Nepal</t>
+          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital - The Rising Nepal</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>NRCS marking 64th anniversary; mobilizes 5,000 volunteers in Bhotekoshi flood-hit area The Rising Nepal</t>
+          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital The Rising Nepal</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5Mb1pfSW80ekw1dkdTRDZoYVhmaHV4LWZBVlZqTXQyb3Y4ZFI4dlptQ3hMbHo3UFdVWTJsMDU1RVAyZTlvSGVvVGRZVFN0SVZG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
         </is>
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5Mb1pfSW80ekw1dkdTRDZoYVhmaHV4LWZBVlZqTXQyb3Y4ZFI4dlptQ3hMbHo3UFdVWTJsMDU1RVAyZTlvSGVvVGRZVFN0SVZG?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -8825,7 +8825,7 @@
     <row r="163" ht="48" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>44d5da90c9532a74</t>
+          <t>02f3fec961d30051</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -8845,22 +8845,22 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood - The Rising Nepal</t>
+          <t>NRCS marking 64th anniversary; mobilizes 5,000 volunteers in Bhotekoshi flood-hit area - The Rising Nepal</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood The Rising Nepal</t>
+          <t>NRCS marking 64th anniversary; mobilizes 5,000 volunteers in Bhotekoshi flood-hit area The Rising Nepal</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5Mb1pfSW80ekw1dkdTRDZoYVhmaHV4LWZBVlZqTXQyb3Y4ZFI4dlptQ3hMbHo3UFdVWTJsMDU1RVAyZTlvSGVvVGRZVFN0SVZG?oc=5</t>
         </is>
       </c>
       <c r="H163" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5Mb1pfSW80ekw1dkdTRDZoYVhmaHV4LWZBVlZqTXQyb3Y4ZFI4dlptQ3hMbHo3UFdVWTJsMDU1RVAyZTlvSGVvVGRZVFN0SVZG?oc=5</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
     <row r="164" ht="48" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>b80549513c064b0f</t>
+          <t>44d5da90c9532a74</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -8887,32 +8887,32 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T04:32:23Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood - Ekantipur</t>
+          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood Ekantipur</t>
+          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">

--- a/downloads/rasuwa-flood-source-metadata.xlsx
+++ b/downloads/rasuwa-flood-source-metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12T20:31:43Z</t>
+          <t>2026-09-12T23:02:12Z</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Generated 2026-09-12T20:31:43Z · 557 records · original URLs remain the authoritative source</t>
+          <t>Generated 2026-09-12T23:02:12Z · 557 records · original URLs remain the authoritative source</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>895a2cd3bab3daaf</t>
+          <t>b24ad7ca0530ad59</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T20:31:43Z</t>
+          <t>2026-09-12T10:43:08Z</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood - english.nepalnews.com</t>
+          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal - The Rising Nepal</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood english.nepalnews.com</t>
+          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal The Rising Nepal</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>9b19a739b91a113a</t>
+          <t>895a2cd3bab3daaf</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -723,32 +723,32 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T10:43:08Z</t>
+          <t>2026-09-12T20:31:43Z</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Damage - Ratopati</t>
+          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood - Nepalnews.com</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Damage Ratopati</t>
+          <t>Nepal faces Rs 723 billion recovery bill after catastrophic Bhote Koshi flood Nepalnews.com</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdTFYcnNZdzYtVkMyVWdkS0oyeU9UcWRDczNRa3lVZnNYcGNobEhCQktiZFViSktBZ296Y093YnJIdnRMLUJYVmtFOEtUUURLN3l4M2pZY3RJYmN5UFh4THpCalZsdnRaZk0wMXExTUpPX2RhcjB0SF9xRzZhR0Q0NkwyTkYyejU1OWRhM3JOSFQ1TFp6VXJfdnNrNGdyMTZudFUydXg0T3ZldDJmTGZKUlZFem5ZelVF?oc=5</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>599e39e4bd45cec7</t>
+          <t>9b19a739b91a113a</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -785,22 +785,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood - Ratopati</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood Damage - Ratopati</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>FAO Preliminary Report on Bhote Koshi Flood Ratopati</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood Damage Ratopati</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMixwFBVV95cUxNWmUtNnhJYmJhM094aF9UaGlnN0lVSVJxS0ZhZ2F6SlF1NkdwYlI3YUwtTVgydDdna01yY3NUQTA0clhseDNVWWk2QU9BXzNIcEJHY0tIZ1ctbXNmX0trOTl2V1ZQUWpkNlk4dlF5aG9hdUJ5YWwxVEtNc040ekxzd2cwYVhQM0s2bUNuLU1iVTE3czB2d0lScmNiM19Ecm8xXzB5RG1PeXNFRDNjWU9kbUViSk5TUXBmdXRFUU03dV9pZDFLZGtR?oc=5</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>b24ad7ca0530ad59</t>
+          <t>599e39e4bd45cec7</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -832,27 +832,27 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Ratopati</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal - The Rising Nepal</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood - Ratopati</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood not just an issue for Nepal, but a global concern: Khanal The Rising Nepal</t>
+          <t>FAO Preliminary Report on Bhote Koshi Flood Ratopati</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1ET1huYjRRSEIzbnRBd0tvRmtIRkZSQ1VTN0dSMkFPM3BwSHB1ZkVEQWFHc2hoUWtEMUloYkRnNzVjNFB1NU9fTzZrb01lOTRQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxQZzZCbERQNjhibzNJQml2RThQLVlTbk1sLTg4clV4Yk12S0Z5a2cteFlQQmNZaExwLW9OX29mT3c1NTNNV3dWbmlfd3loOWNSbDEyMUozTm5JVnRtZWJZTkNDZUZ2X3V3Wnh3b2ZEVHVQVUJKdHF5TVNDakMxeXpKZTlrajRXVlZzbGtTRFg1M0FvYk9kQm1NTzkzQVpaNW5ldDlhRmx6Qm1wN0lBbGFFNGpOeTdWLTJHN1FCUXRCMWtBekE?oc=5</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>thehimalayantimes.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill - The Himalayan Times</t>
+          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill - thehimalayantimes.com</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill The Himalayan Times</t>
+          <t>Bhotekoshi flood leaves Rs 95.42 billion cleanup and recovery bill thehimalayantimes.com</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone - english.khabarhub.com</t>
+          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone - Khabarhub</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone english.khabarhub.com</t>
+          <t>Bhotekoshi flood: Rs 100 billion needed for social sector recovery alone Khabarhub</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,377 - english.khabarhub.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,377 - Khabarhub</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,377 english.khabarhub.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,377 Khabarhub</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>reliefweb.int</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 - ReliefWeb</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 - reliefweb.int</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 ReliefWeb</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 10 September 2026 reliefweb.int</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims - english.khabarhub.com</t>
+          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims english.khabarhub.com</t>
+          <t>Sardikhola residents donate Rs 793,775 to Bhote Koshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing - english.nepalnews.com</t>
+          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing english.nepalnews.com</t>
+          <t>Bhote Koshi flood update: 1,367 bodies recovered, around 5,100 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,367 so far - english.khabarhub.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,367 so far - Khabarhub</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,367 so far english.khabarhub.com</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,367 so far Khabarhub</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -1924,17 +1924,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,357 - english.khabarhub.com</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,357 - Khabarhub</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,357 english.khabarhub.com</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,357 Khabarhub</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -2028,17 +2028,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Subcommittee formed to study economic impact of Rasuwa flood - english.khabarhub.com</t>
+          <t>Subcommittee formed to study economic impact of Rasuwa flood - Khabarhub</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Subcommittee formed to study economic impact of Rasuwa flood english.khabarhub.com</t>
+          <t>Subcommittee formed to study economic impact of Rasuwa flood Khabarhub</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing - english.nepalnews.com</t>
+          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing english.nepalnews.com</t>
+          <t>Bhote Koshi flood: 1,367 confirmed dead, more than 5,100 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll reaches 1,365 - english.khabarhub.com</t>
+          <t>Bhotekoshi flood death toll reaches 1,365 - Khabarhub</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll reaches 1,365 english.khabarhub.com</t>
+          <t>Bhotekoshi flood death toll reaches 1,365 Khabarhub</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage - english.khabarhub.com</t>
+          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage - Khabarhub</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage english.khabarhub.com</t>
+          <t>Finance Minister calls for realistic assessment of Bhote Koshi flood damage Khabarhub</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM - english.nepalnews.com</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM - Nepalnews.com</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM english.nepalnews.com</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,358 as 5,326 remain missing as of 6PM Nepalnews.com</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 600 foreign nationals still missing - english.nepalnews.com</t>
+          <t>Bhote Koshi flood: 600 foreign nationals still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: 600 foreign nationals still missing english.nepalnews.com</t>
+          <t>Bhote Koshi flood: 600 foreign nationals still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -2548,17 +2548,17 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: How big is the damage? A sector-by-sector reckoning - english.nepalnews.com</t>
+          <t>Bhote Koshi flood: How big is the damage? A sector-by-sector reckoning - Nepalnews.com</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: How big is the damage? A sector-by-sector reckoning english.nepalnews.com</t>
+          <t>Bhote Koshi flood: How big is the damage? A sector-by-sector reckoning Nepalnews.com</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims - english.khabarhub.com</t>
+          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims - Khabarhub</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims english.khabarhub.com</t>
+          <t>WorldLink provides Rs 10.1 million for Bhotekoshi flood victims Khabarhub</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,357; over 5,300 still missing - english.nepalnews.com</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,357; over 5,300 still missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll rises to 1,357; over 5,300 still missing english.nepalnews.com</t>
+          <t>Bhote Koshi flood: Death toll rises to 1,357; over 5,300 still missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -2808,17 +2808,17 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims - english.nepalnews.com</t>
+          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims - Nepalnews.com</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims english.nepalnews.com</t>
+          <t>NAIMA provides Rs 5 million to Bhote Koshi flood victims Nepalnews.com</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -2860,17 +2860,17 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>India expresses condolences over loss of lives and property in Bhotekoshi flood - english.khabarhub.com</t>
+          <t>India expresses condolences over loss of lives and property in Bhotekoshi flood - Khabarhub</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>India expresses condolences over loss of lives and property in Bhotekoshi flood english.khabarhub.com</t>
+          <t>India expresses condolences over loss of lives and property in Bhotekoshi flood Khabarhub</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -2912,17 +2912,17 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Tributes paid to Bhotekoshi flood victims with candlelight vigil at Tourism Board - english.khabarhub.com</t>
+          <t>Tributes paid to Bhotekoshi flood victims with candlelight vigil at Tourism Board - Khabarhub</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Tributes paid to Bhotekoshi flood victims with candlelight vigil at Tourism Board english.khabarhub.com</t>
+          <t>Tributes paid to Bhotekoshi flood victims with candlelight vigil at Tourism Board Khabarhub</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact - english.nepalnews.com</t>
+          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact - Nepalnews.com</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact english.nepalnews.com</t>
+          <t>As of 6PM, Bhote Koshi flood death toll reaches 1,356, nearly 5,000 remain out of contact Nepalnews.com</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood - english.khabarhub.com</t>
+          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood - Khabarhub</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood english.khabarhub.com</t>
+          <t>President Paudel urges global action on climate change risks after Bhotekoshi flood Khabarhub</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund - english.nepalnews.com</t>
+          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund - Nepalnews.com</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund english.nepalnews.com</t>
+          <t>Nepali Congress donates Rs 10 million to Bhote Koshi flood relief fund Nepalnews.com</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -3172,17 +3172,17 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood death toll reaches 1,355 - english.khabarhub.com</t>
+          <t>Rasuwa flood death toll reaches 1,355 - Khabarhub</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood death toll reaches 1,355 english.khabarhub.com</t>
+          <t>Rasuwa flood death toll reaches 1,355 Khabarhub</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -3484,17 +3484,17 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital - english.khabarhub.com</t>
+          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital - Khabarhub</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital english.khabarhub.com</t>
+          <t>Bhotekoshi flood: 21 injured receiving treatment at Teaching Hospital Khabarhub</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world - english.khabarhub.com</t>
+          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world - Khabarhub</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world english.khabarhub.com</t>
+          <t>Gagan Thapa urges Nepal to present documented losses from Bhotekoshi flood to the world Khabarhub</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear - english.nepalnews.com</t>
+          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear - Nepalnews.com</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear english.nepalnews.com</t>
+          <t>Bhote Koshi flood: Search intensifies for 600 missing foreigners; Nepal seeks global rescue gear Nepalnews.com</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -3692,17 +3692,17 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification - english.khabarhub.com</t>
+          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification - Khabarhub</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification english.khabarhub.com</t>
+          <t>Bhotekoshi flood: DNA samples collected from 1,181 bodies for identification Khabarhub</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
@@ -3744,17 +3744,17 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital - english.khabarhub.com</t>
+          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital - Khabarhub</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital english.khabarhub.com</t>
+          <t>Bhotekoshi flood: 244 bodies brought to Teaching Hospital Khabarhub</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -3796,17 +3796,17 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>english.khabarhub.com</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts - english.khabarhub.com</t>
+          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts - Khabarhub</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts english.khabarhub.com</t>
+          <t>Bhotekoshi flood: 1,331 bodies recovered in eight districts Khabarhub</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>reliefweb.int</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Nepal Rasuwa Flood Situation Report No. 6 - ReliefWeb</t>
+          <t>Nepal Rasuwa Flood Situation Report No. 6 - reliefweb.int</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Nepal Rasuwa Flood Situation Report No. 6 ReliefWeb</t>
+          <t>Nepal Rasuwa Flood Situation Report No. 6 reliefweb.int</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -3900,17 +3900,17 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>reliefweb.int</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - ReliefWeb</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) - reliefweb.int</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) ReliefWeb</t>
+          <t>Nepal: Rasuwa Flood Situation Report No. 6 (As of 3 September 2026) reliefweb.int</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>reliefweb.int</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) - ReliefWeb</t>
+          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) - reliefweb.int</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) ReliefWeb</t>
+          <t>Nepal: Rasuwa Flood - Flash Appeal (4 September 2026) reliefweb.int</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>The Himalayan Times</t>
+          <t>thehimalayantimes.com</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - The Himalayan Times</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far - thehimalayantimes.com</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far The Himalayan Times</t>
+          <t>Bhotekoshi Flood: 1,290 dead, 8,197 rescued, 4,800 missing so far thehimalayantimes.com</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>english.nepalnews.com</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood disaster: Death toll reaches 1,290; over 4,700 remain missing - english.nepalnews.com</t>
+          <t>Bhote Koshi flood disaster: Death toll reaches 1,290; over 4,700 remain missing - Nepalnews.com</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood disaster: Death toll reaches 1,290; over 4,700 remain missing english.nepalnews.com</t>
+          <t>Bhote Koshi flood disaster: Death toll reaches 1,290; over 4,700 remain missing Nepalnews.com</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>b49f667ad8e744b7</t>
+          <t>8810e59b1c1927f1</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -4363,32 +4363,32 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12T15:29:59Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>reliefweb.int</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myRepublica</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 - reliefweb.int</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myRepublica</t>
+          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 reliefweb.int</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOald4OVY0QWptQU0tam5CR0ZNZVR2NGk0RWNodkE0OHpaRzh0VWZIRVY1ZENQTzYtcExqVHVGbFpVX1JYSC0ta3hrd3g5LWtfdklDQkg2allZbVpudDFKbHprRkwyTkRodWlUcGIzbVYxWGN4VXkxMl9qdHFtTFJvSHBPUGE2Z25jdG5uMzg2YXMzZlVieG5DZzdaS0R3aHhGc3hUYnVoa1Jsdi15R2xBRTlKQ2FKXzBlYXA1Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOR21PU1dCdlZSMmwwTVpaYU5ZVnZmX2xUSVBGaWUwb2Zpc01rZTJmdEhEVm1jdE54WGh3VUZlQ0ZsUnZlV00wNnlOblNfT1NwakVNVnloZWJhNTJCcW9SR3FORThZY19CdHVjWEp3aW1HSE5EUHhldF9wM0tsU0tGSjBaT1hDV2RxaDk5VFc5WWNuOGtyMy1aT1czTEF2VWFLT3E0?oc=5</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivAFBVV95cUxOald4OVY0QWptQU0tam5CR0ZNZVR2NGk0RWNodkE0OHpaRzh0VWZIRVY1ZENQTzYtcExqVHVGbFpVX1JYSC0ta3hrd3g5LWtfdklDQkg2allZbVpudDFKbHprRkwyTkRodWlUcGIzbVYxWGN4VXkxMl9qdHFtTFJvSHBPUGE2Z25jdG5uMzg2YXMzZlVieG5DZzdaS0R3aHhGc3hUYnVoa1Jsdi15R2xBRTlKQ2FKXzBlYXA1Vw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxOR21PU1dCdlZSMmwwTVpaYU5ZVnZmX2xUSVBGaWUwb2Zpc01rZTJmdEhEVm1jdE54WGh3VUZlQ0ZsUnZlV00wNnlOblNfT1NwakVNVnloZWJhNTJCcW9SR3FORThZY19CdHVjWEp3aW1HSE5EUHhldF9wM0tsU0tGSjBaT1hDV2RxaDk5VFc5WWNuOGtyMy1aT1czTEF2VWFLT3E0?oc=5</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>8810e59b1c1927f1</t>
+          <t>40652f6cba568b14</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -4415,32 +4415,32 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T04:29:29Z</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 - ReliefWeb</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>WFP Nepal Situation Report on the Rasuwa Flood Response, 04 September 2026 ReliefWeb</t>
+          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOR21PU1dCdlZSMmwwTVpaYU5ZVnZmX2xUSVBGaWUwb2Zpc01rZTJmdEhEVm1jdE54WGh3VUZlQ0ZsUnZlV00wNnlOblNfT1NwakVNVnloZWJhNTJCcW9SR3FORThZY19CdHVjWEp3aW1HSE5EUHhldF9wM0tsU0tGSjBaT1hDV2RxaDk5VFc5WWNuOGtyMy1aT1czTEF2VWFLT3E0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiowFBVV95cUxOR21PU1dCdlZSMmwwTVpaYU5ZVnZmX2xUSVBGaWUwb2Zpc01rZTJmdEhEVm1jdE54WGh3VUZlQ0ZsUnZlV00wNnlOblNfT1NwakVNVnloZWJhNTJCcW9SR3FORThZY19CdHVjWEp3aW1HSE5EUHhldF9wM0tsU0tGSjBaT1hDV2RxaDk5VFc5WWNuOGtyMy1aT1czTEF2VWFLT3E0?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4457,42 +4457,42 @@
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>40652f6cba568b14</t>
+          <t>c52a95edc1229710</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T04:29:29Z</t>
+          <t>2026-09-03T23:16:04Z</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>nepyork</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' - The Rising Nepal</t>
+          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal - nepyork</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>'Bhotekoshi flood is reminder of grave climate risk' The Rising Nepal</t>
+          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal nepyork</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1uM0E2Q3dJOTV4eHhaTGxIaEowWmNMajRWbEo3OFZEbWpvMU9qRDB1SXh4dElTZ1BlRWR6NHduWWx6ajdPb0x6TDlWSk9paGUz?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>c52a95edc1229710</t>
+          <t>5f76706cec031b28</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
@@ -4519,32 +4519,32 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T23:16:04Z</t>
+          <t>2026-09-08T23:22:50Z</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>nepyork</t>
+          <t>FM Bharat</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal - nepyork</t>
+          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims - FM Bharat</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>New York Nepalis Urge Climate Justice After Deadly Bhote Koshi Flood in Nepal nepyork</t>
+          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims FM Bharat</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxNSko5WWJJRGZkUUtZZjFsS0NpZWJ1RGZ2UFZMZi1wYTl6dk5WdURRSHQwalZoM2pUc1NXTGtJWFBwczRsNWhBVXMtVjRyZndiUFZOemxmSTAyb3p0X1RIbUppbG14QzlYNllyLVdRMXRrQnVRUFBObDQ4TnZDVjlOQk4tY0pld3N2MTFfdUgwMXpySkZNVUwwVkNlU0FZZkctR0ZaRlh6ZkEtcWdoV2c?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4561,7 +4561,7 @@
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>5f76706cec031b28</t>
+          <t>5b6d66ee949b6b7e</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -4571,32 +4571,32 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T23:22:50Z</t>
+          <t>2026-09-03T11:11:13Z</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>FM Bharat</t>
+          <t>The Farsight Nepal</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims - FM Bharat</t>
+          <t>Bhotekoshi flood death toll: 1,252, over 4,200 still missing - The Farsight Nepal</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Nepal govt announces business recovery package for Bhote Koshi flood victims FM Bharat</t>
+          <t>Bhotekoshi flood death toll: 1,252, over 4,200 still missing The Farsight Nepal</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNc3FHMHlXeC1tRDlnbDBmUHVreTZ4V3FBYjlHQzlhR2FaXzlZbnY4QXZKVTAzQUl1RXZIaFJGQy0yTHl4Um1MUm1FOVV6NGxqR1JlUG1ZVXBUQUV5anljSXhIMVdWeXd1RnUycVluRGpRaTdiak1Vd2trQnFkaHpUZ3NyeFlWYTNBeEw4dmM4N04yZw?oc=5</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirwFBVV95cUxNTEdqUnN6cl9SUXJBOUhYLU9MVmItX2RtNVQySXdQZEdXWHVISjZ5S3FydDVsaU5lMklrcV9NSzJsMzcwcU9aSC1nVUpsLVZjQ1JFTEtnWXVjY2lnR1hJbDBuTUs0MG9KWnZjMTZZS0dqeUYzdS02aHJxajVrcENPczlVTGhLNkF6Z3gyRklxcUxmZEpsY0xOa0N6d0Y2cnVlODJCZFV0WHNCNXJfNG8w?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikgFBVV95cUxNc3FHMHlXeC1tRDlnbDBmUHVreTZ4V3FBYjlHQzlhR2FaXzlZbnY4QXZKVTAzQUl1RXZIaFJGQy0yTHl4Um1MUm1FOVV6NGxqR1JlUG1ZVXBUQUV5anljSXhIMVdWeXd1RnUycVluRGpRaTdiak1Vd2trQnFkaHpUZ3NyeFlWYTNBeEw4dmM4N04yZw?oc=5</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4613,7 +4613,7 @@
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>5b6d66ee949b6b7e</t>
+          <t>06e9d4415d0f0371</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T11:11:13Z</t>
+          <t>2026-09-07T19:08:33Z</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>farsightnepal.com</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll: 1,252, over 4,200 still missing - farsightnepal.com</t>
+          <t>How Much International Aid Arrived After the Bhotekoshi Flood? - Ekantipur</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood death toll: 1,252, over 4,200 still missing farsightnepal.com</t>
+          <t>How Much International Aid Arrived After the Bhotekoshi Flood? Ekantipur</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNc3FHMHlXeC1tRDlnbDBmUHVreTZ4V3FBYjlHQzlhR2FaXzlZbnY4QXZKVTAzQUl1RXZIaFJGQy0yTHl4Um1MUm1FOVV6NGxqR1JlUG1ZVXBUQUV5anljSXhIMVdWeXd1RnUycVluRGpRaTdiak1Vd2trQnFkaHpUZ3NyeFlWYTNBeEw4dmM4N04yZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMikgFBVV95cUxNc3FHMHlXeC1tRDlnbDBmUHVreTZ4V3FBYjlHQzlhR2FaXzlZbnY4QXZKVTAzQUl1RXZIaFJGQy0yTHl4Um1MUm1FOVV6NGxqR1JlUG1ZVXBUQUV5anljSXhIMVdWeXd1RnUycVluRGpRaTdiak1Vd2trQnFkaHpUZ3NyeFlWYTNBeEw4dmM4N04yZw?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4665,7 +4665,7 @@
     <row r="83" ht="48" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>06e9d4415d0f0371</t>
+          <t>af5a4a18108fca1c</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -4675,32 +4675,32 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07T19:08:33Z</t>
+          <t>2026-09-03T16:23:58Z</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>How Much International Aid Arrived After the Bhotekoshi Flood? - Ekantipur</t>
+          <t>Nepal weighing options to relocate Bhotekoshi flood survivors - kathmandupost.com</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>How Much International Aid Arrived After the Bhotekoshi Flood? Ekantipur</t>
+          <t>Nepal weighing options to relocate Bhotekoshi flood survivors kathmandupost.com</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMioAFBVV95cUxPWm9McU5DVFlya0dsSnZqS3NEcmtYbjlxREZ5dzJEczhETUI4N3E2TXNlM29fVHhJUVZ5Q2RTOHNVeEpqdFZQWlJLZDl1bm5FRUpkZy1raXhwZV9JREhXTm5Pb05GemNnOVVPZ1NJOFI4QVh6QmdtdGlqZVpMVVA1ZmhPSVIxcDRVYXJYVThJZGxKMHlCQy0xdnZrREQ4X0E3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>af5a4a18108fca1c</t>
+          <t>87b993bb5da00f7f</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T16:23:58Z</t>
+          <t>2026-09-03T11:11:13Z</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>Onlinekhabar English</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Nepal weighing options to relocate Bhotekoshi flood survivors - The Kathmandu Post</t>
+          <t>Gagan Thapa urges public to help Rasuwa flood victims, avoid harsh words - Onlinekhabar English</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Nepal weighing options to relocate Bhotekoshi flood survivors The Kathmandu Post</t>
+          <t>Gagan Thapa urges public to help Rasuwa flood victims, avoid harsh words Onlinekhabar English</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPWFRmYzN6RldPNUVjMk9wcW02QlRZQnRNU0xxOXhmaEdLOVJZZm5RNWlYV0gxTVZwaGMwbHRVXzAwdWJZM28tT1U5REZ6ZFJINklra2xHdENyaUpDaFJPRUZVcWtGOUNyZkd0TlUtUTVNcXQyWm8xd1hKZC1XUHhTcW5UWDB2RzI1S1JkUWJWb0JqalhjT1lUdlZSZXZzM0xJM1dCT01hTzhYQnlGNGc?oc=5</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTFZHYXRHMTJLc3JTRHQtZ0drT2p0VzNWNENEQnJBR2dZS1Eyb3Etam9ncWU4V0tqNnRTVWhxX1JWY09Bb0stcHhMaGNkQjVveXYxNDFncFNHMjE4bTIweWxlc19yQzd6R3UweWZrOTJrZE1mNlY1RWdVekoydzdnWWduTy0zbWlWMFlyTUFrcWdIeWIyR3Fva3JTTFZuZzl5VWZVQ0wzS2UtamM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxPWFRmYzN6RldPNUVjMk9wcW02QlRZQnRNU0xxOXhmaEdLOVJZZm5RNWlYV0gxTVZwaGMwbHRVXzAwdWJZM28tT1U5REZ6ZFJINklra2xHdENyaUpDaFJPRUZVcWtGOUNyZkd0TlUtUTVNcXQyWm8xd1hKZC1XUHhTcW5UWDB2RzI1S1JkUWJWb0JqalhjT1lUdlZSZXZzM0xJM1dCT01hTzhYQnlGNGc?oc=5</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4784,17 +4784,17 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>School students cut snack money to help Bhotekoshi flood victims - The Kathmandu Post</t>
+          <t>School students cut snack money to help Bhotekoshi flood victims - kathmandupost.com</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>School students cut snack money to help Bhotekoshi flood victims The Kathmandu Post</t>
+          <t>School students cut snack money to help Bhotekoshi flood victims kathmandupost.com</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -4836,17 +4836,17 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>They escaped the 2015 earthquake. They couldn’t escape the Bhotekoshi flood - The Kathmandu Post</t>
+          <t>They escaped the 2015 earthquake. They couldn’t escape the Bhotekoshi flood - kathmandupost.com</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>They escaped the 2015 earthquake. They couldn’t escape the Bhotekoshi flood The Kathmandu Post</t>
+          <t>They escaped the 2015 earthquake. They couldn’t escape the Bhotekoshi flood kathmandupost.com</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>thetourismtimes.com</t>
+          <t>The Tourism Times</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood causes over Rs 50 billion tourism damage: Tourism Minister - thetourismtimes.com</t>
+          <t>Rasuwa flood causes over Rs 50 billion tourism damage: Tourism Minister - The Tourism Times</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood causes over Rs 50 billion tourism damage: Tourism Minister thetourismtimes.com</t>
+          <t>Rasuwa flood causes over Rs 50 billion tourism damage: Tourism Minister The Tourism Times</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -5148,17 +5148,17 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 903 - The Kathmandu Post</t>
+          <t>Death toll from Bhotekoshi flood reaches 903 - kathmandupost.com</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 903 The Kathmandu Post</t>
+          <t>Death toll from Bhotekoshi flood reaches 903 kathmandupost.com</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 734 - The Kathmandu Post</t>
+          <t>Death toll from Bhotekoshi flood reaches 734 - kathmandupost.com</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood reaches 734 The Kathmandu Post</t>
+          <t>Death toll from Bhotekoshi flood reaches 734 kathmandupost.com</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Updates: Bhotekoshi flood toll reaches 626 as 2,426 remain unaccounted for - The Kathmandu Post</t>
+          <t>Updates: Bhotekoshi flood toll reaches 626 as 2,426 remain unaccounted for - kathmandupost.com</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Updates: Bhotekoshi flood toll reaches 626 as 2,426 remain unaccounted for The Kathmandu Post</t>
+          <t>Updates: Bhotekoshi flood toll reaches 626 as 2,426 remain unaccounted for kathmandupost.com</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -5408,17 +5408,17 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>What triggered the Rasuwa flood? Scientists piece together a complex chain of events - The Kathmandu Post</t>
+          <t>What triggered the Rasuwa flood? Scientists piece together a complex chain of events - kathmandupost.com</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>What triggered the Rasuwa flood? Scientists piece together a complex chain of events The Kathmandu Post</t>
+          <t>What triggered the Rasuwa flood? Scientists piece together a complex chain of events kathmandupost.com</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>ReliefWeb</t>
+          <t>reliefweb.int</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Satellite-Detected Newly Formed Barrier Lakes Following an Ice-Rock Avalanche in Rasuwa District, Nepal, as of 28 August 2026 (Imagery Analysis: 26&amp;27/08/2026 Published: 27/08/2026 V1) ReliefWeb</t>
+          <t>Satellite-Detected Newly Formed Barrier Lakes Following an Ice-Rock Avalanche in Rasuwa District, Nepal, as of 28 August 2026 (Imagery Analysis: 26&amp;27/08/2026 Published: 27/08/2026 V1) reliefweb.int</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: What happened in Himalayas and what comes next? - The Kathmandu Post</t>
+          <t>Bhotekoshi flood: What happened in Himalayas and what comes next? - kathmandupost.com</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: What happened in Himalayas and what comes next? The Kathmandu Post</t>
+          <t>Bhotekoshi flood: What happened in Himalayas and what comes next? kathmandupost.com</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
@@ -5616,17 +5616,17 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>How the Bhotekoshi flood unfolded over 10 hours - The Kathmandu Post</t>
+          <t>How the Bhotekoshi flood unfolded over 10 hours - kathmandupost.com</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>How the Bhotekoshi flood unfolded over 10 hours The Kathmandu Post</t>
+          <t>How the Bhotekoshi flood unfolded over 10 hours kathmandupost.com</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>826 out of contact after Bhotekoshi flood, including 590 tourists - The Kathmandu Post</t>
+          <t>826 out of contact after Bhotekoshi flood, including 590 tourists - kathmandupost.com</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>826 out of contact after Bhotekoshi flood, including 590 tourists The Kathmandu Post</t>
+          <t>826 out of contact after Bhotekoshi flood, including 590 tourists kathmandupost.com</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -5980,17 +5980,17 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood - The Kathmandu Post</t>
+          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood - kathmandupost.com</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood The Kathmandu Post</t>
+          <t>Ice avalanche, debris lake may have triggered Bhotekoshi flood kathmandupost.com</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
@@ -6032,17 +6032,17 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: What we know, what remains unclear - The Kathmandu Post</t>
+          <t>Bhotekoshi flood: What we know, what remains unclear - kathmandupost.com</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: What we know, what remains unclear The Kathmandu Post</t>
+          <t>Bhotekoshi flood: What we know, what remains unclear kathmandupost.com</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -6084,17 +6084,17 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>UPDATE: Rasuwa flood death toll climbs to 95 as dozens remain missing - The Kathmandu Post</t>
+          <t>UPDATE: Rasuwa flood death toll climbs to 95 as dozens remain missing - kathmandupost.com</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>UPDATE: Rasuwa flood death toll climbs to 95 as dozens remain missing The Kathmandu Post</t>
+          <t>UPDATE: Rasuwa flood death toll climbs to 95 as dozens remain missing kathmandupost.com</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
@@ -6136,17 +6136,17 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>UPDATE: Rasuwa flood death toll climbs to 22 as dozens remain missing - The Kathmandu Post</t>
+          <t>UPDATE: Rasuwa flood death toll climbs to 22 as dozens remain missing - kathmandupost.com</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>UPDATE: Rasuwa flood death toll climbs to 22 as dozens remain missing The Kathmandu Post</t>
+          <t>UPDATE: Rasuwa flood death toll climbs to 22 as dozens remain missing kathmandupost.com</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
@@ -6240,17 +6240,17 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>In Photos: Bhotekoshi flood leaves a trail of destruction - The Kathmandu Post</t>
+          <t>In Photos: Bhotekoshi flood leaves a trail of destruction - kathmandupost.com</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>In Photos: Bhotekoshi flood leaves a trail of destruction The Kathmandu Post</t>
+          <t>In Photos: Bhotekoshi flood leaves a trail of destruction kathmandupost.com</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>thetourismtimes.com</t>
+          <t>The Tourism Times</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Hundreds, including foreign tourists, remain out of contact after Bhote Koshi flood mayhem - thetourismtimes.com</t>
+          <t>Hundreds, including foreign tourists, remain out of contact after Bhote Koshi flood mayhem - The Tourism Times</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Hundreds, including foreign tourists, remain out of contact after Bhote Koshi flood mayhem thetourismtimes.com</t>
+          <t>Hundreds, including foreign tourists, remain out of contact after Bhote Koshi flood mayhem The Tourism Times</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
@@ -6344,17 +6344,17 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Scientists suspect ice avalanche triggered Bhotekoshi flood - The Kathmandu Post</t>
+          <t>Scientists suspect ice avalanche triggered Bhotekoshi flood - kathmandupost.com</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Scientists suspect ice avalanche triggered Bhotekoshi flood The Kathmandu Post</t>
+          <t>Scientists suspect ice avalanche triggered Bhotekoshi flood kathmandupost.com</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
@@ -6396,17 +6396,17 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>The Kathmandu Post</t>
+          <t>kathmandupost.com</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>What we know about the Bhotekoshi flood so far - The Kathmandu Post</t>
+          <t>What we know about the Bhotekoshi flood so far - kathmandupost.com</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>What we know about the Bhotekoshi flood so far The Kathmandu Post</t>
+          <t>What we know about the Bhotekoshi flood so far kathmandupost.com</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
@@ -8877,7 +8877,7 @@
     <row r="164" ht="48" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>2c151d9781807ab6</t>
+          <t>b49f667ad8e744b7</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
@@ -8887,32 +8887,32 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-12T15:29:59Z</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital - The Rising Nepal</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood - myRepublica</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital The Rising Nepal</t>
+          <t>1,344 bodies recovered, 4,898 remain missing in Bhotekoshi Flood myRepublica</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOald4OVY0QWptQU0tam5CR0ZNZVR2NGk0RWNodkE0OHpaRzh0VWZIRVY1ZENQTzYtcExqVHVGbFpVX1JYSC0ta3hrd3g5LWtfdklDQkg2allZbVpudDFKbHprRkwyTkRodWlUcGIzbVYxWGN4VXkxMl9qdHFtTFJvSHBPUGE2Z25jdG5uMzg2YXMzZlVieG5DZzdaS0R3aHhGc3hUYnVoa1Jsdi15R2xBRTlKQ2FKXzBlYXA1Vw?oc=5</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivAFBVV95cUxOald4OVY0QWptQU0tam5CR0ZNZVR2NGk0RWNodkE0OHpaRzh0VWZIRVY1ZENQTzYtcExqVHVGbFpVX1JYSC0ta3hrd3g5LWtfdklDQkg2allZbVpudDFKbHprRkwyTkRodWlUcGIzbVYxWGN4VXkxMl9qdHFtTFJvSHBPUGE2Z25jdG5uMzg2YXMzZlVieG5DZzdaS0R3aHhGc3hUYnVoa1Jsdi15R2xBRTlKQ2FKXzBlYXA1Vw?oc=5</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -8929,7 +8929,7 @@
     <row r="165" ht="48" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>6c94171fc3f8e00c</t>
+          <t>2c151d9781807ab6</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 - The Rising Nepal</t>
+          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital - The Rising Nepal</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 The Rising Nepal</t>
+          <t>Minister Dr. Timilsina visits Bhotekoshi flood victims in hospital The Rising Nepal</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
         </is>
       </c>
       <c r="H165" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1DejVwY1RpLXJvNC1LcEhQU1hZTVFzZUdfY0pteWJLN2dSTTF6OUNUUUJLaFRkQUtsbGxDRVlWY1VxU0loRGp3YTFPUm91QzJp?oc=5</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -8981,7 +8981,7 @@
     <row r="166" ht="48" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>b80549513c064b0f</t>
+          <t>6c94171fc3f8e00c</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
@@ -8991,32 +8991,32 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T04:32:23Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Ekantipur</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood - Ekantipur</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 - The Rising Nepal</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood Ekantipur</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 The Rising Nepal</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9SQlpyazZhVGgwQ1NKNDlKMThwMEM0emlPS0gwcFNHeVRSZGhxNDcwek5rU0dYTk5mYWVOcHlSdWowWFhFMWxKalZvczl5dzlU?oc=5</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -9033,7 +9033,7 @@
     <row r="167" ht="48" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>44d5da90c9532a74</t>
+          <t>b80549513c064b0f</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
@@ -9043,32 +9043,32 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-08T04:32:23Z</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Ekantipur</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood - The Rising Nepal</t>
+          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood - Ekantipur</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood The Rising Nepal</t>
+          <t>Repair work begins on 20 suspension bridges damaged by the Bhotekoshi flood Ekantipur</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
         </is>
       </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuwFBVV95cUxNUnBKSmJWWTdiVlh2OENPNWRMTzVMZGJ1d2JsZk4yTkk0bl9NSlNtX2pfTUg4elV2SHRkM0s3d252bGJMbmU5c2ZzZzVKNnBGcVNwRVg5YU5RdHF3eXY0cDl3aWZaLUlpaFdiU3dNdWRfaG9jY240Wll1WUh0YXp0VW9mcmEzR3AwOVVqSlhVbjBNUG1EM0d2Q1lvVE5sSTZGLXdQc2pXM25LVm1LSkJYREhkdjhWSmVxUGY4?oc=5</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="168" ht="48" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>e5d64e09de0bd232</t>
+          <t>44d5da90c9532a74</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:11:26Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -9105,22 +9105,22 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Portugal-based Nepali chef donates Rs 5.1 million to Bhotekoshi flood victims - The Rising Nepal</t>
+          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Portugal-based Nepali chef donates Rs 5.1 million to Bhotekoshi flood victims The Rising Nepal</t>
+          <t>Govt continues search and rescue operations on tenth day of devastating Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tZzdIUWFTb2MxM2dJRjRDdW9iQUJlMzdpc1dOdW9jWFZEWkF3QVJnQXBNdnU2bGltTHZITUc0Z3hTV3ZGOG10Q3V3eFRDUkdf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
         </is>
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tZzdIUWFTb2MxM2dJRjRDdW9iQUJlMzdpc1dOdW9jWFZEWkF3QVJnQXBNdnU2bGltTHZITUc0Z3hTV3ZGOG10Q3V3eFRDUkdf?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5PQkJGQ1V6YVV4UVRUb054TGNNZ0ExZmhnUWZhamdMUkxNSEE4Mjc2LUIySE1ZbXJqMVBWXzFCSXpYWVFQWnBMTHVuYXZ5ZTQz?oc=5</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -9137,7 +9137,7 @@
     <row r="169" ht="48" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>5e55f5bee3be9088</t>
+          <t>e5d64e09de0bd232</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
@@ -9147,32 +9147,32 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T21:07:58Z</t>
+          <t>2026-09-05T15:11:26Z</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myRepublica</t>
+          <t>Portugal-based Nepali chef donates Rs 5.1 million to Bhotekoshi flood victims - The Rising Nepal</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myRepublica</t>
+          <t>Portugal-based Nepali chef donates Rs 5.1 million to Bhotekoshi flood victims The Rising Nepal</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOMDI2RHpZaWZkNEdlNTFxUkRFSTJqbHU4aTFNYnB1aU1uSVZnczhKV0IxWVlCbW1YQTNXSmlJbzVaTkM2Tnh6eGNVZEM4WmJsOVhyd1R0SmdzTWxMYWlBNUJibkMzbGIwdWhHd2dPTWNsdXVRcTZ3b2NZeU9pUFI4VnE5WmVuZWtoODE0dDF2NnFWTWd0dndpbWZRUFo3TnBMQ1cwQ0dITEVvM1p0Uk5VLVNGMUFiWXVmQUtTZFhNbHRxaWlUUWhZcDVsaUM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tZzdIUWFTb2MxM2dJRjRDdW9iQUJlMzdpc1dOdW9jWFZEWkF3QVJnQXBNdnU2bGltTHZITUc0Z3hTV3ZGOG10Q3V3eFRDUkdf?oc=5</t>
         </is>
       </c>
       <c r="H169" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizAFBVV95cUxOMDI2RHpZaWZkNEdlNTFxUkRFSTJqbHU4aTFNYnB1aU1uSVZnczhKV0IxWVlCbW1YQTNXSmlJbzVaTkM2Tnh6eGNVZEM4WmJsOVhyd1R0SmdzTWxMYWlBNUJibkMzbGIwdWhHd2dPTWNsdXVRcTZ3b2NZeU9pUFI4VnE5WmVuZWtoODE0dDF2NnFWTWd0dndpbWZRUFo3TnBMQ1cwQ0dITEVvM1p0Uk5VLVNGMUFiWXVmQUtTZFhNbHRxaWlUUWhZcDVsaUM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1tZzdIUWFTb2MxM2dJRjRDdW9iQUJlMzdpc1dOdW9jWFZEWkF3QVJnQXBNdnU2bGltTHZITUc0Z3hTV3ZGOG10Q3V3eFRDUkdf?oc=5</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -9189,7 +9189,7 @@
     <row r="170" ht="48" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>d85a94e8900b3070</t>
+          <t>5e55f5bee3be9088</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-08T21:07:58Z</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -9209,22 +9209,22 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything - myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myRepublica</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myRepublica</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPYjk2ZGJNZ1F2S2JlWUJhYUphOExqSXljUjJYN0UyWGpjNk5hNjlsUlhjSEZsbnE5Q3h0aW4yd0FiWXB1d2tyUkdxekVFaDY5dFljU2xOSmVEbUtpQW84YzN3bHV0N0pDNWNlc09vdDFVVHh5Q3VXMjJOTFBPNE1nay1EVndFeldvei0yOEZNRWhKOFYyeHBsMzhLRVpJc0FKYVU0UVdOVHNEZFdOM1pscG9CNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOMDI2RHpZaWZkNEdlNTFxUkRFSTJqbHU4aTFNYnB1aU1uSVZnczhKV0IxWVlCbW1YQTNXSmlJbzVaTkM2Tnh6eGNVZEM4WmJsOVhyd1R0SmdzTWxMYWlBNUJibkMzbGIwdWhHd2dPTWNsdXVRcTZ3b2NZeU9pUFI4VnE5WmVuZWtoODE0dDF2NnFWTWd0dndpbWZRUFo3TnBMQ1cwQ0dITEVvM1p0Uk5VLVNGMUFiWXVmQUtTZFhNbHRxaWlUUWhZcDVsaUM?oc=5</t>
         </is>
       </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxPYjk2ZGJNZ1F2S2JlWUJhYUphOExqSXljUjJYN0UyWGpjNk5hNjlsUlhjSEZsbnE5Q3h0aW4yd0FiWXB1d2tyUkdxekVFaDY5dFljU2xOSmVEbUtpQW84YzN3bHV0N0pDNWNlc09vdDFVVHh5Q3VXMjJOTFBPNE1nay1EVndFeldvei0yOEZNRWhKOFYyeHBsMzhLRVpJc0FKYVU0UVdOVHNEZFdOM1pscG9CNA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMizAFBVV95cUxOMDI2RHpZaWZkNEdlNTFxUkRFSTJqbHU4aTFNYnB1aU1uSVZnczhKV0IxWVlCbW1YQTNXSmlJbzVaTkM2Tnh6eGNVZEM4WmJsOVhyd1R0SmdzTWxMYWlBNUJibkMzbGIwdWhHd2dPTWNsdXVRcTZ3b2NZeU9pUFI4VnE5WmVuZWtoODE0dDF2NnFWTWd0dndpbWZRUFo3TnBMQ1cwQ0dITEVvM1p0Uk5VLVNGMUFiWXVmQUtTZFhNbHRxaWlUUWhZcDVsaUM?oc=5</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -9241,7 +9241,7 @@
     <row r="171" ht="48" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>258c222aa846d3dc</t>
+          <t>d85a94e8900b3070</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:42Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -9261,22 +9261,22 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary - myRepublica</t>
+          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything - myRepublica</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary myRepublica</t>
+          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything myRepublica</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPYjk2ZGJNZ1F2S2JlWUJhYUphOExqSXljUjJYN0UyWGpjNk5hNjlsUlhjSEZsbnE5Q3h0aW4yd0FiWXB1d2tyUkdxekVFaDY5dFljU2xOSmVEbUtpQW84YzN3bHV0N0pDNWNlc09vdDFVVHh5Q3VXMjJOTFBPNE1nay1EVndFeldvei0yOEZNRWhKOFYyeHBsMzhLRVpJc0FKYVU0UVdOVHNEZFdOM1pscG9CNA?oc=5</t>
         </is>
       </c>
       <c r="H171" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiswFBVV95cUxPYjk2ZGJNZ1F2S2JlWUJhYUphOExqSXljUjJYN0UyWGpjNk5hNjlsUlhjSEZsbnE5Q3h0aW4yd0FiWXB1d2tyUkdxekVFaDY5dFljU2xOSmVEbUtpQW84YzN3bHV0N0pDNWNlc09vdDFVVHh5Q3VXMjJOTFBPNE1nay1EVndFeldvei0yOEZNRWhKOFYyeHBsMzhLRVpJc0FKYVU0UVdOVHNEZFdOM1pscG9CNA?oc=5</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -9293,7 +9293,7 @@
     <row r="172" ht="48" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>830f7a3c5e28048a</t>
+          <t>258c222aa846d3dc</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-08T11:15:42Z</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -9313,22 +9313,22 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 1,287 dead bodies recovered, more than 13,000 people rescued - myRepublica</t>
+          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary - myRepublica</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 1,287 dead bodies recovered, more than 13,000 people rescued myRepublica</t>
+          <t>NRCS mobilizes 5,000 volunteers in Bhotekoshi flood-hit area as it marks 64th anniversary myRepublica</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPeUktTzEwQnZ2dVJoV1hPZ2Z4MmZDSlBYcG9tMFh6aXhFcm82Q1k3STRXMTRyTjB3QkstbFppVVZGaVVrZ3JCQmh5UXViY3ptaGZwVGpUSEl3cTJmZERTdWpKSmRsanZySXlLeldVcEx5SjFZSExHZFYyQ0E1VXd3WXI2cU1pUlpaYUExZnRhNENydk9abXp2MXdHaGwtby02MHFRbHNKZkRORGhkZDhKU0JVaHhBY1RBaklZUjcwQ0NkNjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPeUktTzEwQnZ2dVJoV1hPZ2Z4MmZDSlBYcG9tMFh6aXhFcm82Q1k3STRXMTRyTjB3QkstbFppVVZGaVVrZ3JCQmh5UXViY3ptaGZwVGpUSEl3cTJmZERTdWpKSmRsanZySXlLeldVcEx5SjFZSExHZFYyQ0E1VXd3WXI2cU1pUlpaYUExZnRhNENydk9abXp2MXdHaGwtby02MHFRbHNKZkRORGhkZDhKU0JVaHhBY1RBaklZUjcwQ0NkNjg?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxOdlZ4dG5NNHhQOEF3NVplUXdTMDdlUF9yd1FFM3VGMkg3TDgyeXUxelNKYzNQYkVyS1ZXam9SVms4VlVYODdTVjhPdmZOd2NLUmMxekoxeWlaVVhyNm5MZ1NiS251enFFRXRLOTBzXzdpZkRJMkxwLTd3Zm9IZzdfeXpnbHdPTDlCQ3RGemg5cVhYcWJtMFZWZEVwNEpGNW1Ob1ZicHF6LUNjZ1gwdWhxak9VZmtPT1FVLTZyeWswbG9CNTIyMVFkNE9n?oc=5</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="173" ht="48" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>95216a0448be4ecd</t>
+          <t>830f7a3c5e28048a</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -9365,22 +9365,22 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myRepublica</t>
+          <t>Rasuwa flood: 1,287 dead bodies recovered, more than 13,000 people rescued - myRepublica</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myRepublica</t>
+          <t>Rasuwa flood: 1,287 dead bodies recovered, more than 13,000 people rescued myRepublica</t>
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPeUktTzEwQnZ2dVJoV1hPZ2Z4MmZDSlBYcG9tMFh6aXhFcm82Q1k3STRXMTRyTjB3QkstbFppVVZGaVVrZ3JCQmh5UXViY3ptaGZwVGpUSEl3cTJmZERTdWpKSmRsanZySXlLeldVcEx5SjFZSExHZFYyQ0E1VXd3WXI2cU1pUlpaYUExZnRhNENydk9abXp2MXdHaGwtby02MHFRbHNKZkRORGhkZDhKU0JVaHhBY1RBaklZUjcwQ0NkNjg?oc=5</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiwwFBVV95cUxPeUktTzEwQnZ2dVJoV1hPZ2Z4MmZDSlBYcG9tMFh6aXhFcm82Q1k3STRXMTRyTjB3QkstbFppVVZGaVVrZ3JCQmh5UXViY3ptaGZwVGpUSEl3cTJmZERTdWpKSmRsanZySXlLeldVcEx5SjFZSExHZFYyQ0E1VXd3WXI2cU1pUlpaYUExZnRhNENydk9abXp2MXdHaGwtby02MHFRbHNKZkRORGhkZDhKU0JVaHhBY1RBaklZUjcwQ0NkNjg?oc=5</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -9397,7 +9397,7 @@
     <row r="174" ht="48" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>48d3e154be99628d</t>
+          <t>95216a0448be4ecd</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T23:02:25Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>The Annapurna Express</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>India sends sixth, seventh consignments of relief supplies for Bhotekoshi flood survivors - The Annapurna Express</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing - myRepublica</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>India sends sixth, seventh consignments of relief supplies for Bhotekoshi flood survivors The Annapurna Express</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,293; 4798 remain missing myRepublica</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE4tcG54NDZtTktIb2ZZczBVblc0Wnk0dkNfbGJEMFN1aDI3aEZYd29lbEljeF9jdVdRdkwzd1hFcXduNkNUdG12am9BbnduOHYxMGdOLUtDWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTE4tcG54NDZtTktIb2ZZczBVblc0Wnk0dkNfbGJEMFN1aDI3aEZYd29lbEljeF9jdVdRdkwzd1hFcXduNkNUdG12am9BbnduOHYxMGdOLUtDWQ?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivwFBVV95cUxPa2ZSbHE0R09nSDJkb2Z2ZTIyaDNFbUpScXR6ZDdyM0phdjlFX0dNalB3ZEU2TWY3RkZZM2NiNHJab2pPdEFVZFlXWGxLMWloMXBvQlVVeHYzb1lLVXNPN0hxOXBweFY0bE9sNmdsTEVjTUN3UlVMXzdyRUdFUm83Z2dxZ0xhNUIxcEVHRVdkOXlPOHV6TkpUYXFkaFZhVVNVeEhZSGF3eFhBWm45S2s0R1ZEWk9vRjZxTlNsM0ZNSQ?oc=5</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="175" ht="48" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>c887d95a53da880f</t>
+          <t>48d3e154be99628d</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
@@ -9459,32 +9459,32 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-04T23:02:25Z</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>The Annapurna Express</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Heavy rain forecast in Bhote Koshi flood affected area - Nepalnews.com</t>
+          <t>India sends sixth, seventh consignments of relief supplies for Bhotekoshi flood survivors - The Annapurna Express</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Heavy rain forecast in Bhote Koshi flood affected area Nepalnews.com</t>
+          <t>India sends sixth, seventh consignments of relief supplies for Bhotekoshi flood survivors The Annapurna Express</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNUTFsUm5kQnd1VTA3TjZVRFhXVUM5WDNwQzVUZkM4d25fQVhGWm9YVl9FVDc5amJReHFuamJvdnhBYWNGU3ptazhkdzE3ZnRndnJ5ZUltcWp6c0lxYjk1UnlPdzRMTlRlU04tM0l2NHJ6bi1QdTdzaktXelR2OE1aXy1DWEZ0b19SX1gwQ1U2T2FVZFE3VFZRbGZlMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE4tcG54NDZtTktIb2ZZczBVblc0Wnk0dkNfbGJEMFN1aDI3aEZYd29lbEljeF9jdVdRdkwzd1hFcXduNkNUdG12am9BbnduOHYxMGdOLUtDWQ?oc=5</t>
         </is>
       </c>
       <c r="H175" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNUTFsUm5kQnd1VTA3TjZVRFhXVUM5WDNwQzVUZkM4d25fQVhGWm9YVl9FVDc5amJReHFuamJvdnhBYWNGU3ptazhkdzE3ZnRndnJ5ZUltcWp6c0lxYjk1UnlPdzRMTlRlU04tM0l2NHJ6bi1QdTdzaktXelR2OE1aXy1DWEZ0b19SX1gwQ1U2T2FVZFE3VFZRbGZlMA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiV0FVX3lxTE4tcG54NDZtTktIb2ZZczBVblc0Wnk0dkNfbGJEMFN1aDI3aEZYd29lbEljeF9jdVdRdkwzd1hFcXduNkNUdG12am9BbnduOHYxMGdOLUtDWQ?oc=5</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -9501,7 +9501,7 @@
     <row r="176" ht="48" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>1cd5958711f2fd98</t>
+          <t>c887d95a53da880f</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
@@ -9521,22 +9521,22 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA CEO Jensen Huang donates Rs 1.5 billion for Bhote Koshi flood relief - Nepalnews.com</t>
+          <t>Heavy rain forecast in Bhote Koshi flood affected area - Nepalnews.com</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA CEO Jensen Huang donates Rs 1.5 billion for Bhote Koshi flood relief Nepalnews.com</t>
+          <t>Heavy rain forecast in Bhote Koshi flood affected area Nepalnews.com</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNbTFfVTJJM2YzcXFIYWRIZnlRX1pVLWpScFRzQ1U5cnZlTUNyR3Z5ajdpRk83U2RsTl9OWFdGWUt3Q3dpNkdxckdTZUdXeGN0cXBPbnJFYmh6QkhramNQTEFNcFhUT1NBY1luSm9NMmZHV1dycDNnX0JZLURoVFdJQlA1OUlFdnU5bFhSMzNoTldjeGk2Nmt6dzNhNlA5RlNGUlVWT1JQSF9mLUJzWUM4Q18tYjFsbDludHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNUTFsUm5kQnd1VTA3TjZVRFhXVUM5WDNwQzVUZkM4d25fQVhGWm9YVl9FVDc5amJReHFuamJvdnhBYWNGU3ptazhkdzE3ZnRndnJ5ZUltcWp6c0lxYjk1UnlPdzRMTlRlU04tM0l2NHJ6bi1QdTdzaktXelR2OE1aXy1DWEZ0b19SX1gwQ1U2T2FVZFE3VFZRbGZlMA?oc=5</t>
         </is>
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxNbTFfVTJJM2YzcXFIYWRIZnlRX1pVLWpScFRzQ1U5cnZlTUNyR3Z5ajdpRk83U2RsTl9OWFdGWUt3Q3dpNkdxckdTZUdXeGN0cXBPbnJFYmh6QkhramNQTEFNcFhUT1NBY1luSm9NMmZHV1dycDNnX0JZLURoVFdJQlA1OUlFdnU5bFhSMzNoTldjeGk2Nmt6dzNhNlA5RlNGUlVWT1JQSF9mLUJzWUM4Q18tYjFsbDludHc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMimwFBVV95cUxNUTFsUm5kQnd1VTA3TjZVRFhXVUM5WDNwQzVUZkM4d25fQVhGWm9YVl9FVDc5amJReHFuamJvdnhBYWNGU3ptazhkdzE3ZnRndnJ5ZUltcWp6c0lxYjk1UnlPdzRMTlRlU04tM0l2NHJ6bi1QdTdzaktXelR2OE1aXy1DWEZ0b19SX1gwQ1U2T2FVZFE3VFZRbGZlMA?oc=5</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -9553,7 +9553,7 @@
     <row r="177" ht="48" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>69c5156e1e556a67</t>
+          <t>1cd5958711f2fd98</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
@@ -9563,32 +9563,32 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims - myRepublica</t>
+          <t>NVIDIA CEO Jensen Huang donates Rs 1.5 billion for Bhote Koshi flood relief - Nepalnews.com</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims myRepublica</t>
+          <t>NVIDIA CEO Jensen Huang donates Rs 1.5 billion for Bhote Koshi flood relief Nepalnews.com</t>
         </is>
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNbTFfVTJJM2YzcXFIYWRIZnlRX1pVLWpScFRzQ1U5cnZlTUNyR3Z5ajdpRk83U2RsTl9OWFdGWUt3Q3dpNkdxckdTZUdXeGN0cXBPbnJFYmh6QkhramNQTEFNcFhUT1NBY1luSm9NMmZHV1dycDNnX0JZLURoVFdJQlA1OUlFdnU5bFhSMzNoTldjeGk2Nmt6dzNhNlA5RlNGUlVWT1JQSF9mLUJzWUM4Q18tYjFsbDludHc?oc=5</t>
         </is>
       </c>
       <c r="H177" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiugFBVV95cUxNbTFfVTJJM2YzcXFIYWRIZnlRX1pVLWpScFRzQ1U5cnZlTUNyR3Z5ajdpRk83U2RsTl9OWFdGWUt3Q3dpNkdxckdTZUdXeGN0cXBPbnJFYmh6QkhramNQTEFNcFhUT1NBY1luSm9NMmZHV1dycDNnX0JZLURoVFdJQlA1OUlFdnU5bFhSMzNoTldjeGk2Nmt6dzNhNlA5RlNGUlVWT1JQSF9mLUJzWUM4Q18tYjFsbDludHc?oc=5</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -9605,7 +9605,7 @@
     <row r="178" ht="48" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>68b706a9a3354119</t>
+          <t>69c5156e1e556a67</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -9625,22 +9625,22 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 193 bodies brought to Teaching Hospital, 24 identified - myRepublica</t>
+          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Rasuwa flood: 193 bodies brought to Teaching Hospital, 24 identified myRepublica</t>
+          <t>Minister Timilsina urges media to protect dignity, privacy of Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNS0JMTVlWaDY1NW42TUlicDR0VTUyX3ZTcEljUW9tVzRQT1VZTEMzNnBQT0tZeW8zUlY5Sks1RXNZaE1uSmQtU0VqMXRfZU1XbEJXQWZNRjBxWnRBSU9DNjRDdmZMcmlJUUc2Q0w0c0xkQ28zQ2FKNEk1djJOV2padlAzRVB4NDdWUHlYSjJ3RFU0OTFpeGZJRXRGbzg1MGk3RGhTUlJOdThGeE5jVlFPNUVhR3J5RURWc052dEJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
         </is>
       </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNS0JMTVlWaDY1NW42TUlicDR0VTUyX3ZTcEljUW9tVzRQT1VZTEMzNnBQT0tZeW8zUlY5Sks1RXNZaE1uSmQtU0VqMXRfZU1XbEJXQWZNRjBxWnRBSU9DNjRDdmZMcmlJUUc2Q0w0c0xkQ28zQ2FKNEk1djJOV2padlAzRVB4NDdWUHlYSjJ3RFU0OTFpeGZJRXRGbzg1MGk3RGhTUlJOdThGeE5jVlFPNUVhR3J5RURWc052dEJR?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNU0ZxakdpQTlWM3gtbXA5R1BCclp5M0dyQVBBeG0wb0RkSDVRdHRmbVNSVU8wbWt4NDZnLS1KZVNQWHFPa1NzWWg5RHppQ0VJWk9RN0pMMFNmZGdNNG5MamNWUF82TjV1ZG1Rcmpfb3QwT1RYZlg0bnJpWVg2RDBXaURleDBwVWk3VmlqQXlETEJDaHdfWWh5N3VpcDNSaUdGSTExZ2hVM0xyZGVoSXdEdXNTNDNYUlNuNTlOdExVbUlRSVg2bWNOUWVR?oc=5</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -9657,7 +9657,7 @@
     <row r="179" ht="48" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>e6746450786fdf1d</t>
+          <t>68b706a9a3354119</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Nepalnews.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,293 as rescue operations continue - Nepalnews.com</t>
+          <t>Rasuwa flood: 193 bodies brought to Teaching Hospital, 24 identified - myRepublica</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi flood: Death toll reaches 1,293 as rescue operations continue Nepalnews.com</t>
+          <t>Rasuwa flood: 193 bodies brought to Teaching Hospital, 24 identified myRepublica</t>
         </is>
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNQmpDbElfZU9ZWk1tN1dIRlBoSzJua3hOZFV0OUp5WTYxbkh6RDMyaXhMYzI1X19vaEkyd0czSy1PN2taSElpbDBfVk9jWTFtUmJRcy1scUp4UVVMTE14Y3JWNzl5VXc5b04wZ0Y3N2RQRzlYOWNCLW9GRVdKR3JBcHNMNXN2XzRIUFQxS2pWUUE5bEhKcF9IcW5pYzE4QXNYbzJIU1F2MF8xNDVtdjFTOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNS0JMTVlWaDY1NW42TUlicDR0VTUyX3ZTcEljUW9tVzRQT1VZTEMzNnBQT0tZeW8zUlY5Sks1RXNZaE1uSmQtU0VqMXRfZU1XbEJXQWZNRjBxWnRBSU9DNjRDdmZMcmlJUUc2Q0w0c0xkQ28zQ2FKNEk1djJOV2padlAzRVB4NDdWUHlYSjJ3RFU0OTFpeGZJRXRGbzg1MGk3RGhTUlJOdThGeE5jVlFPNUVhR3J5RURWc052dEJR?oc=5</t>
         </is>
       </c>
       <c r="H179" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxNQmpDbElfZU9ZWk1tN1dIRlBoSzJua3hOZFV0OUp5WTYxbkh6RDMyaXhMYzI1X19vaEkyd0czSy1PN2taSElpbDBfVk9jWTFtUmJRcy1scUp4UVVMTE14Y3JWNzl5VXc5b04wZ0Y3N2RQRzlYOWNCLW9GRVdKR3JBcHNMNXN2XzRIUFQxS2pWUUE5bEhKcF9IcW5pYzE4QXNYbzJIU1F2MF8xNDVtdjFTOA?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMivgFBVV95cUxNS0JMTVlWaDY1NW42TUlicDR0VTUyX3ZTcEljUW9tVzRQT1VZTEMzNnBQT0tZeW8zUlY5Sks1RXNZaE1uSmQtU0VqMXRfZU1XbEJXQWZNRjBxWnRBSU9DNjRDdmZMcmlJUUc2Q0w0c0xkQ28zQ2FKNEk1djJOV2padlAzRVB4NDdWUHlYSjJ3RFU0OTFpeGZJRXRGbzg1MGk3RGhTUlJOdThGeE5jVlFPNUVhR3J5RURWc052dEJR?oc=5</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -9709,7 +9709,7 @@
     <row r="180" ht="48" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>51205720cf66f904</t>
+          <t>e6746450786fdf1d</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
@@ -9719,32 +9719,32 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>Nepalnews.com</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Govt continues search and rescue operations - Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,293 as rescue operations continue - Nepalnews.com</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Govt continues search and rescue operations Khabarhub</t>
+          <t>Bhote Koshi flood: Death toll reaches 1,293 as rescue operations continue Nepalnews.com</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWTGlQb2FrZXhkM0pEU0lnb3NNSUc0LTNvNHhubFNIaWFHREJvejAyNVpRUUVZXzdsbGxESkcyWUxRd3ZINmdycEc2X09Held3MkFFSnhrWmI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNQmpDbElfZU9ZWk1tN1dIRlBoSzJua3hOZFV0OUp5WTYxbkh6RDMyaXhMYzI1X19vaEkyd0czSy1PN2taSElpbDBfVk9jWTFtUmJRcy1scUp4UVVMTE14Y3JWNzl5VXc5b04wZ0Y3N2RQRzlYOWNCLW9GRVdKR3JBcHNMNXN2XzRIUFQxS2pWUUE5bEhKcF9IcW5pYzE4QXNYbzJIU1F2MF8xNDVtdjFTOA?oc=5</t>
         </is>
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWTGlQb2FrZXhkM0pEU0lnb3NNSUc0LTNvNHhubFNIaWFHREJvejAyNVpRUUVZXzdsbGxESkcyWUxRd3ZINmdycEc2X09Held3MkFFSnhrWmI?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMisAFBVV95cUxNQmpDbElfZU9ZWk1tN1dIRlBoSzJua3hOZFV0OUp5WTYxbkh6RDMyaXhMYzI1X19vaEkyd0czSy1PN2taSElpbDBfVk9jWTFtUmJRcy1scUp4UVVMTE14Y3JWNzl5VXc5b04wZ0Y3N2RQRzlYOWNCLW9GRVdKR3JBcHNMNXN2XzRIUFQxS2pWUUE5bEhKcF9IcW5pYzE4QXNYbzJIU1F2MF8xNDVtdjFTOA?oc=5</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -9761,7 +9761,7 @@
     <row r="181" ht="48" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t>8a2301952fd337c9</t>
+          <t>51205720cf66f904</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
@@ -9771,32 +9771,32 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Nepal demands urgent climate funds after Bhotekoshi flood - The Rising Nepal</t>
+          <t>Bhotekoshi flood: Govt continues search and rescue operations - Khabarhub</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Nepal demands urgent climate funds after Bhotekoshi flood The Rising Nepal</t>
+          <t>Bhotekoshi flood: Govt continues search and rescue operations Khabarhub</t>
         </is>
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sTkktd1dCcmR1aUxTN1o3eTdYTDVXWGhjRERDTWxLZ3ZVOFdSUHRsanBqQnBIb0l2bDN5UC16U2dvM29RcnBoMWpBR1lydHB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWTGlQb2FrZXhkM0pEU0lnb3NNSUc0LTNvNHhubFNIaWFHREJvejAyNVpRUUVZXzdsbGxESkcyWUxRd3ZINmdycEc2X09Held3MkFFSnhrWmI?oc=5</t>
         </is>
       </c>
       <c r="H181" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sTkktd1dCcmR1aUxTN1o3eTdYTDVXWGhjRERDTWxLZ3ZVOFdSUHRsanBqQnBIb0l2bDN5UC16U2dvM29RcnBoMWpBR1lydHB3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWTGlQb2FrZXhkM0pEU0lnb3NNSUc0LTNvNHhubFNIaWFHREJvejAyNVpRUUVZXzdsbGxESkcyWUxRd3ZINmdycEc2X09Held3MkFFSnhrWmI?oc=5</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -9813,7 +9813,7 @@
     <row r="182" ht="48" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
         <is>
-          <t>8d6e2ecb2368dfef</t>
+          <t>8a2301952fd337c9</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
@@ -9823,32 +9823,32 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>2026-09-06T04:35:51Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything - myRepublica</t>
+          <t>Nepal demands urgent climate funds after Bhotekoshi flood - The Rising Nepal</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything myRepublica</t>
+          <t>Nepal demands urgent climate funds after Bhotekoshi flood The Rising Nepal</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORDJDdHFRZi1zYV8xWFdXVDBPOUF4bVNYX0ZJblBROFczT1lsN28zeF9pLUUwLUVRRFlCYmdQT0pnR3RpbzFpOS1yLTNOeU5faXEwV09wdklLMDlaMElET242MVhWQVBOT1FfMm92Q2l0NXhoUVBfY3M4ZEFFa1M1TC1aTWw1dE9aNkc1empTRmxLZE13Y285ZzZqTjNBVjJNanNiZkpSbnBzOXhFN1NWWm9zallmYmxO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sTkktd1dCcmR1aUxTN1o3eTdYTDVXWGhjRERDTWxLZ3ZVOFdSUHRsanBqQnBIb0l2bDN5UC16U2dvM29RcnBoMWpBR1lydHB3?oc=5</t>
         </is>
       </c>
       <c r="H182" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxORDJDdHFRZi1zYV8xWFdXVDBPOUF4bVNYX0ZJblBROFczT1lsN28zeF9pLUUwLUVRRFlCYmdQT0pnR3RpbzFpOS1yLTNOeU5faXEwV09wdklLMDlaMElET242MVhWQVBOT1FfMm92Q2l0NXhoUVBfY3M4ZEFFa1M1TC1aTWw1dE9aNkc1empTRmxLZE13Y285ZzZqTjNBVjJNanNiZkpSbnBzOXhFN1NWWm9zallmYmxO?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sTkktd1dCcmR1aUxTN1o3eTdYTDVXWGhjRERDTWxLZ3ZVOFdSUHRsanBqQnBIb0l2bDN5UC16U2dvM29RcnBoMWpBR1lydHB3?oc=5</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="183" ht="48" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>bcfd74891234047d</t>
+          <t>8d6e2ecb2368dfef</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
@@ -9875,32 +9875,32 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-06T04:35:51Z</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Communication Minister urges sensitivity in reporting Bhotekoshi flood victims - radionepalonline.com</t>
+          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything - myRepublica</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Communication Minister urges sensitivity in reporting Bhotekoshi flood victims radionepalonline.com</t>
+          <t>Bhote Koshi Flood: Ten Minutes That Could Change Everything myRepublica</t>
         </is>
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1OX3M4Q0NiS2NfMGN4bnVPbW9nQnV6MkdwN2dWN2JadVVucnRhOE9DaXM1dEd0S3VsUERMZ2VaTlAwZnVIbTluYU95aVZqOUwzLUpoMG42UTBncHZwMUlKTU9ob0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORDJDdHFRZi1zYV8xWFdXVDBPOUF4bVNYX0ZJblBROFczT1lsN28zeF9pLUUwLUVRRFlCYmdQT0pnR3RpbzFpOS1yLTNOeU5faXEwV09wdklLMDlaMElET242MVhWQVBOT1FfMm92Q2l0NXhoUVBfY3M4ZEFFa1M1TC1aTWw1dE9aNkc1empTRmxLZE13Y285ZzZqTjNBVjJNanNiZkpSbnBzOXhFN1NWWm9zallmYmxO?oc=5</t>
         </is>
       </c>
       <c r="H183" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE1OX3M4Q0NiS2NfMGN4bnVPbW9nQnV6MkdwN2dWN2JadVVucnRhOE9DaXM1dEd0S3VsUERMZ2VaTlAwZnVIbTluYU95aVZqOUwzLUpoMG42UTBncHZwMUlKTU9ob0E?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiuAFBVV95cUxORDJDdHFRZi1zYV8xWFdXVDBPOUF4bVNYX0ZJblBROFczT1lsN28zeF9pLUUwLUVRRFlCYmdQT0pnR3RpbzFpOS1yLTNOeU5faXEwV09wdklLMDlaMElET242MVhWQVBOT1FfMm92Q2l0NXhoUVBfY3M4ZEFFa1M1TC1aTWw1dE9aNkc1empTRmxLZE13Y285ZzZqTjNBVjJNanNiZkpSbnBzOXhFN1NWWm9zallmYmxO?oc=5</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -9917,7 +9917,7 @@
     <row r="184" ht="48" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
         <is>
-          <t>15b1509ca084c43e</t>
+          <t>bcfd74891234047d</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T16:19:49Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -9937,22 +9937,22 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
+          <t>Communication Minister urges sensitivity in reporting Bhotekoshi flood victims - radionepalonline.com</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Death toll from Bhotekoshi flood climbs to 1,290 so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
+          <t>Communication Minister urges sensitivity in reporting Bhotekoshi flood victims radionepalonline.com</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBGRXFkTnM0SloyX19aMHVnakJhT3cwSkRYd3BzNU9VbnhORkFjNENtY19LcmtWVE5lTEpLaEloaXNWT2pLbmdRUWdWNUlRTjZCVm0zdGozMEV0M0l3eGdScWE0SWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1OX3M4Q0NiS2NfMGN4bnVPbW9nQnV6MkdwN2dWN2JadVVucnRhOE9DaXM1dEd0S3VsUERMZ2VaTlAwZnVIbTluYU95aVZqOUwzLUpoMG42UTBncHZwMUlKTU9ob0E?oc=5</t>
         </is>
       </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBGRXFkTnM0SloyX19aMHVnakJhT3cwSkRYd3BzNU9VbnhORkFjNENtY19LcmtWVE5lTEpLaEloaXNWT2pLbmdRUWdWNUlRTjZCVm0zdGozMEV0M0l3eGdScWE0SWc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE1OX3M4Q0NiS2NfMGN4bnVPbW9nQnV6MkdwN2dWN2JadVVucnRhOE9DaXM1dEd0S3VsUERMZ2VaTlAwZnVIbTluYU95aVZqOUwzLUpoMG42UTBncHZwMUlKTU9ob0E?oc=5</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="185" ht="48" customHeight="1">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t>2f51aada7d65b122</t>
+          <t>15b1509ca084c43e</t>
         </is>
       </c>
       <c r="B185" s="8" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05T10:32:39Z</t>
+          <t>2026-09-04T16:19:49Z</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>myRepublica</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina visits hospital to check health of Bhotekoshi flood victims - myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 so far – Public Service Broadcasting, Radio Nepal - radionepalonline.com</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Minister Timilsina visits hospital to check health of Bhotekoshi flood victims myRepublica</t>
+          <t>Death toll from Bhotekoshi flood climbs to 1,290 so far – Public Service Broadcasting, Radio Nepal radionepalonline.com</t>
         </is>
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMUowRzJnTl8xdURUb1RZc2twR3M5Nk1iWHdoQ0ZJRG9JY3RPNThqaGQ2aGZ1VDBLUGwzUVctT001N1E0bktNLXhqTkNkMi01T2NHVllBeVRNZ1lYYVIyT3BFUGhfb0Z3bDFJdzh3UVVycFZqN0FNV1czRWIyaVZCSEl4YlRja19PQ21aenJQZVFoUFhoUUYtUlVZV1BFcUlDT1JrN0d1RlFKQnZvYTBITEFfalVYX3BsQmtYTmU2YjBHRXBDMXZHZnV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBGRXFkTnM0SloyX19aMHVnakJhT3cwSkRYd3BzNU9VbnhORkFjNENtY19LcmtWVE5lTEpLaEloaXNWT2pLbmdRUWdWNUlRTjZCVm0zdGozMEV0M0l3eGdScWE0SWc?oc=5</t>
         </is>
       </c>
       <c r="H185" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNMUowRzJnTl8xdURUb1RZc2twR3M5Nk1iWHdoQ0ZJRG9JY3RPNThqaGQ2aGZ1VDBLUGwzUVctT001N1E0bktNLXhqTkNkMi01T2NHVllBeVRNZ1lYYVIyT3BFUGhfb0Z3bDFJdzh3UVVycFZqN0FNV1czRWIyaVZCSEl4YlRja19PQ21aenJQZVFoUFhoUUYtUlVZV1BFcUlDT1JrN0d1RlFKQnZvYTBITEFfalVYX3BsQmtYTmU2YjBHRXBDMXZHZnV3?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTFBGRXFkTnM0SloyX19aMHVnakJhT3cwSkRYd3BzNU9VbnhORkFjNENtY19LcmtWVE5lTEpLaEloaXNWT2pLbmdRUWdWNUlRTjZCVm0zdGozMEV0M0l3eGdScWE0SWc?oc=5</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
     <row r="186" ht="48" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t>b81c16b925a58806</t>
+          <t>2f51aada7d65b122</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
@@ -10036,27 +10036,27 @@
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>english.ratopati.com</t>
+          <t>myRepublica</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Relatives Perform Funeral Rites with Kush Effigies for Those Missing in Bhote Koshi Flood - english.ratopati.com</t>
+          <t>Minister Timilsina visits hospital to check health of Bhotekoshi flood victims - myRepublica</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Relatives Perform Funeral Rites with Kush Effigies for Those Missing in Bhote Koshi Flood english.ratopati.com</t>
+          <t>Minister Timilsina visits hospital to check health of Bhotekoshi flood victims myRepublica</t>
         </is>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1IWW9IZFkxWHp2TzFEaFJIWkUyR08zdEtEd2J0elhSSEg3WjBQSTlUb0RIQ28wdkJuaVN5YXhKQ0hBeDNWNmZaMjIwd0ROS2I0ZjFldVE0NllVdC1maGlTNTI5VWxJQTQ3SndYS3ZOTmU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMUowRzJnTl8xdURUb1RZc2twR3M5Nk1iWHdoQ0ZJRG9JY3RPNThqaGQ2aGZ1VDBLUGwzUVctT001N1E0bktNLXhqTkNkMi01T2NHVllBeVRNZ1lYYVIyT3BFUGhfb0Z3bDFJdzh3UVVycFZqN0FNV1czRWIyaVZCSEl4YlRja19PQ21aenJQZVFoUFhoUUYtUlVZV1BFcUlDT1JrN0d1RlFKQnZvYTBITEFfalVYX3BsQmtYTmU2YjBHRXBDMXZHZnV3?oc=5</t>
         </is>
       </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTE1IWW9IZFkxWHp2TzFEaFJIWkUyR08zdEtEd2J0elhSSEg3WjBQSTlUb0RIQ28wdkJuaVN5YXhKQ0hBeDNWNmZaMjIwd0ROS2I0ZjFldVE0NllVdC1maGlTNTI5VWxJQTQ3SndYS3ZOTmU?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiygFBVV95cUxNMUowRzJnTl8xdURUb1RZc2twR3M5Nk1iWHdoQ0ZJRG9JY3RPNThqaGQ2aGZ1VDBLUGwzUVctT001N1E0bktNLXhqTkNkMi01T2NHVllBeVRNZ1lYYVIyT3BFUGhfb0Z3bDFJdzh3UVVycFZqN0FNV1czRWIyaVZCSEl4YlRja19PQ21aenJQZVFoUFhoUUYtUlVZV1BFcUlDT1JrN0d1RlFKQnZvYTBITEFfalVYX3BsQmtYTmU2YjBHRXBDMXZHZnV3?oc=5</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -10073,7 +10073,7 @@
     <row r="187" ht="48" customHeight="1">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>3f458a24f691b6af</t>
+          <t>b81c16b925a58806</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -10083,32 +10083,32 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:44:14Z</t>
+          <t>2026-09-05T10:32:39Z</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>english.ratopati.com</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Search and rescue continuous in Trishuli-3 'A' - The Rising Nepal</t>
+          <t>Relatives Perform Funeral Rites with Kush Effigies for Those Missing in Bhote Koshi Flood - english.ratopati.com</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Search and rescue continuous in Trishuli-3 'A' The Rising Nepal</t>
+          <t>Relatives Perform Funeral Rites with Kush Effigies for Those Missing in Bhote Koshi Flood english.ratopati.com</t>
         </is>
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9RbWFwM1c4UU10YkZCT3BfN094Nk4yYV9QaVBHYkxvc0VYTEhqMm1VQjA4S192TmxNZVZBWGZKcFFHTXNLMFd2bm9fbUdOczNm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1IWW9IZFkxWHp2TzFEaFJIWkUyR08zdEtEd2J0elhSSEg3WjBQSTlUb0RIQ28wdkJuaVN5YXhKQ0hBeDNWNmZaMjIwd0ROS2I0ZjFldVE0NllVdC1maGlTNTI5VWxJQTQ3SndYS3ZOTmU?oc=5</t>
         </is>
       </c>
       <c r="H187" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9RbWFwM1c4UU10YkZCT3BfN094Nk4yYV9QaVBHYkxvc0VYTEhqMm1VQjA4S192TmxNZVZBWGZKcFFHTXNLMFd2bm9fbUdOczNm?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMicEFVX3lxTE1IWW9IZFkxWHp2TzFEaFJIWkUyR08zdEtEd2J0elhSSEg3WjBQSTlUb0RIQ28wdkJuaVN5YXhKQ0hBeDNWNmZaMjIwd0ROS2I0ZjFldVE0NllVdC1maGlTNTI5VWxJQTQ3SndYS3ZOTmU?oc=5</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="188" ht="48" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>86d22dfe0810a933</t>
+          <t>3f458a24f691b6af</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
@@ -10140,27 +10140,27 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>radionepalonline.com</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Heavy rain forecast in Bhotekoshi flood-affected area, authorities urge caution - radionepalonline.com</t>
+          <t>Bhotekoshi flood: Search and rescue continuous in Trishuli-3 'A' - The Rising Nepal</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Heavy rain forecast in Bhotekoshi flood-affected area, authorities urge caution radionepalonline.com</t>
+          <t>Bhotekoshi flood: Search and rescue continuous in Trishuli-3 'A' The Rising Nepal</t>
         </is>
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE51d0RwbmpDNjdKaEp2b1pTbFF1ajNhMzMta3ZNSHJ5TnMzQk9wQnZjWUFLcTk0QmtOV1J4djBOOHItc19fcldXV1BDSHprWkZmNUtGM1UwY2ZOWGdPVnh3M3pQTmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9RbWFwM1c4UU10YkZCT3BfN094Nk4yYV9QaVBHYkxvc0VYTEhqMm1VQjA4S192TmxNZVZBWGZKcFFHTXNLMFd2bm9fbUdOczNm?oc=5</t>
         </is>
       </c>
       <c r="H188" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE51d0RwbmpDNjdKaEp2b1pTbFF1ajNhMzMta3ZNSHJ5TnMzQk9wQnZjWUFLcTk0QmtOV1J4djBOOHItc19fcldXV1BDSHprWkZmNUtGM1UwY2ZOWGdPVnh3M3pQTmM?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE9RbWFwM1c4UU10YkZCT3BfN094Nk4yYV9QaVBHYkxvc0VYTEhqMm1VQjA4S192TmxNZVZBWGZKcFFHTXNLMFd2bm9fbUdOczNm?oc=5</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
@@ -10177,7 +10177,7 @@
     <row r="189" ht="48" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>ca7286e595d52280</t>
+          <t>86d22dfe0810a933</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -10192,27 +10192,27 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Khabarhub</t>
+          <t>radionepalonline.com</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,325 - Khabarhub</t>
+          <t>Heavy rain forecast in Bhotekoshi flood-affected area, authorities urge caution - radionepalonline.com</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: Death toll reaches 1,325 Khabarhub</t>
+          <t>Heavy rain forecast in Bhotekoshi flood-affected area, authorities urge caution radionepalonline.com</t>
         </is>
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWV1U5REY5bkk2ekF0TmxacTBKdW5Oc3E3TkxQVzUyRHlQZmJjUVhvdDB6NUZvMTFNMkNaR0pDa1FUa0dnc0lXZDVDaTFTX2MxUmlCcjN2cEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE51d0RwbmpDNjdKaEp2b1pTbFF1ajNhMzMta3ZNSHJ5TnMzQk9wQnZjWUFLcTk0QmtOV1J4djBOOHItc19fcldXV1BDSHprWkZmNUtGM1UwY2ZOWGdPVnh3M3pQTmM?oc=5</t>
         </is>
       </c>
       <c r="H189" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWV1U5REY5bkk2ekF0TmxacTBKdW5Oc3E3TkxQVzUyRHlQZmJjUVhvdDB6NUZvMTFNMkNaR0pDa1FUa0dnc0lXZDVDaTFTX2MxUmlCcjN2cEk?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiZEFVX3lxTE51d0RwbmpDNjdKaEp2b1pTbFF1ajNhMzMta3ZNSHJ5TnMzQk9wQnZjWUFLcTk0QmtOV1J4djBOOHItc19fcldXV1BDSHprWkZmNUtGM1UwY2ZOWGdPVnh3M3pQTmM?oc=5</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="190" ht="48" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>856502028ad6525f</t>
+          <t>ca7286e595d52280</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
@@ -10239,32 +10239,32 @@
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:22:45Z</t>
+          <t>2026-09-04T20:44:14Z</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>The Rising Nepal</t>
+          <t>Khabarhub</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA testing process begins to identify bodies - The Rising Nepal</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,325 - Khabarhub</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Bhotekoshi flood: DNA testing process begins to identify bodies The Rising Nepal</t>
+          <t>Bhotekoshi flood: Death toll reaches 1,325 Khabarhub</t>
         </is>
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBSS0F2WlpfNjZHUUdyRm9iTlM0X1RreTVGLW9PZFYyTEFISl9lcDhxVFVDWkQ0aS1hUW1ENXZSUU1GX2pZZ0V0YXVLVHB2T285?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWV1U5REY5bkk2ekF0TmxacTBKdW5Oc3E3TkxQVzUyRHlQZmJjUVhvdDB6NUZvMTFNMkNaR0pDa1FUa0dnc0lXZDVDaTFTX2MxUmlCcjN2cEk?oc=5</t>
         </is>
       </c>
       <c r="H190" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTFBSS0F2WlpfNjZHUUdyRm9iTlM0X1RreTVGLW9PZFYyTEFISl9lcDhxVFVDWkQ0aS1hUW1ENXZSUU1GX2pZZ0V0YXVLVHB2T285?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiWEFVX3lxTFBWV1U5REY5bkk2ekF0TmxacTBKdW5Oc3E3TkxQVzUyRHlQZmJjUVhvdDB6NUZvMTFNMkNaR0pDa1FUa0dnc0lXZDVDaTFTX2MxUmlCcjN2cEk?oc=5</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -10281,7 +10281,7 @@
     <row r="191" ht="48" customHeight="1">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>d1d4dff918ddaa2a</t>
+          <t>856502028ad6525f</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04T11:15:05Z</t>
+          <t>2026-09-02T14:22:45Z</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -10301,22 +10301,22 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh aids one million USD for Bhotekoshi flood affected - The Rising Nepal</t>
+          <t>Bhotekoshi flood: DNA testing process begins to identify bodies - The Rising Nepal</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh aids one million USD for Bhotekoshi flood affected The Rising Nepal</t>
+          <t>Bhotekoshi flood: DNA testing process begins to identify bodies The Rising Nepal</t>
         </is>
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5sRkhWMFd4U3cxSjVKbmNzQzdRamhzQTgxTVlIcnRvaUJrUHUzRzJvWEZpQlZGMUpybmx3Unc5LXBQSGd1YU85MERRSGdvb3pP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBSS0F2WlpfNjZHUUdyRm9iTlM0X1RreTVGLW9PZFYyTEFISl9lcDhxVFVDWkQ0aS1hUW1ENXZSUU1GX2pZZ0V0YXVLVHB2T285?oc=5</t>
         </is>
       </c>
       <c r="H191" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5sRkhWMFd4U3cxSjVKbmNzQzdRamhzQTgxTVlIcnRvaUJrUHUzRzJvWEZpQlZGMUpybmx3Unc5LXBQSGd1YU85MERRSGdvb3pP?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTFBSS0F2WlpfNjZHUUdyRm9iTlM0X1RreTVGLW9PZFYyTEFISl9lcDhxVFVDWkQ0aS1hUW1ENXZSUU1GX2pZZ0V0YXVLVHB2T285?oc=5</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -10333,42 +10333,42 @@
     <row r="192" ht="48" customHeight="1">
       <c r="A192" s="8" t="inlineStr">
         <is>
-          <t>87b993bb5da00f7f</t>
+          <t>d1d4dff918ddaa2a</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03T11:11:13Z</t>
+          <t>2026-09-04T11:15:05Z</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Onlinekhabar English</t>
+          <t>The Rising Nepal</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Gagan Thapa urges public to help Rasuwa flood victims, avoid harsh words - Onlinekhabar English</t>
+          <t>Bangladesh aids one million USD for Bhotekoshi flood affected - The Rising Nepal</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Gagan Thapa urges public to help Rasuwa flood victims, avoid harsh words Onlinekhabar English</t>
+          <t>Bangladesh aids one million USD for Bhotekoshi flood affected The Rising Nepal</t>
         </is>
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPWFRmYzN6RldPNUVjMk9wcW02QlRZQnRNU0xxOXhmaEdLOVJZZm5RNWlYV0gxTVZwaGMwbHRVXzAwdWJZM28tT1U5REZ6ZFJINklra2xHdENyaUpDaFJPRUZVcWtGOUNyZkd0TlUtUTVNcXQyWm8xd1hKZC1XUHhTcW5UWDB2RzI1S1JkUWJWb0JqalhjT1lUdlZSZXZzM0xJM1dCT01hTzhYQnlGNGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE5sRkhWMFd4U3cxSjVKbmNzQzdRamhzQTgxTVlIcnRvaUJrUHUzRzJvWEZpQlZGMUpybmx3Unc5LXBQSGd1YU85MERRSGdvb3pP?oc=5</t>
         </is>
       </c>
       <c r="H192" s="8" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMirgFBVV95cUxPWFRmYzN6RldPNUVjMk9wcW02QlRZQnRNU0xxOXhmaEdLOVJZZm5RNWlYV0gxTVZwaGMwbHRVXzAwdWJZM28tT1U5REZ6ZFJINklra2xHdENyaUpDaFJPRUZVcWtGOUNyZkd0TlUtUTVNcXQyWm8xd1hKZC1XUHhTcW5UWDB2RzI1S1JkUWJWb0JqalhjT1lUdlZSZXZzM0xJM1dCT01hTzhYQnlGNGc?oc=5</t>
+          <t>https://web.archive.org/web/*/https://news.google.com/rss/articles/CBMiUEFVX3lxTE5sRkhWMFd4U3cxSjVKbmNzQzdRamhzQTgxTVlIcnRvaUJrUHUzRzJvWEZpQlZGMUpybmx3Unc5LXBQSGd1YU85MERRSGdvb3pP?oc=5</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
